--- a/data/hrm_sync_actual_1.xlsx
+++ b/data/hrm_sync_actual_1.xlsx
@@ -70,79 +70,400 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02224288</t>
+  </si>
+  <si>
+    <t>Võ Văn Dương</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bonbin</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 3</t>
+  </si>
+  <si>
+    <t>03/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>03/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02021159</t>
+  </si>
+  <si>
+    <t>Trần Vương</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 2</t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
+  </si>
+  <si>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất : ca 1</t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 2</t>
+  </si>
+  <si>
+    <t>02516134</t>
+  </si>
+  <si>
+    <t>Ngô Xuân Nghĩa</t>
+  </si>
+  <si>
+    <t>Thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>Lớn hơn KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
+  </si>
+  <si>
+    <t>02022158</t>
+  </si>
+  <si>
+    <t>Bùi Lê Đức Minh</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 3)</t>
+  </si>
+  <si>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
     <t>02229894</t>
   </si>
   <si>
     <t>Nguyễn Hữu Tài</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
     <t>tăng ca hỗ trợ sản xuất ca1</t>
   </si>
   <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
     <t>12/09/2026 06:00:00</t>
   </si>
   <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Bằng KH</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>02222785</t>
-  </si>
-  <si>
-    <t>Nguyễn Anh Duy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
+    <t>02022149</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Mạnh</t>
+  </si>
+  <si>
+    <t>thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>10/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>10/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 2)</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
   </si>
   <si>
     <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
   </si>
   <si>
-    <t>19/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>20/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca 1</t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02022158</t>
-  </si>
-  <si>
-    <t>Bùi Lê Đức Minh</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất(ca 3)</t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
+  </si>
+  <si>
+    <t>09/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 19:30:00</t>
+  </si>
+  <si>
+    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
+  </si>
+  <si>
+    <t>09/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca3 </t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất(ca2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gian tiếp</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca2</t>
+  </si>
+  <si>
+    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
+  </si>
+  <si>
+    <t>02325295</t>
+  </si>
+  <si>
+    <t>Lưu Văn Đủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
+  </si>
+  <si>
+    <t>hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>16/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bobin</t>
+  </si>
+  <si>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hổ trợ sản xuất </t>
   </si>
   <si>
     <t>02325301</t>
@@ -151,61 +472,67 @@
     <t>Cao Thế Mỹ</t>
   </si>
   <si>
-    <t xml:space="preserve">tăng ca sản xuất </t>
-  </si>
-  <si>
-    <t>02241656</t>
-  </si>
-  <si>
-    <t>Lương Trọng Ân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca3 </t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất(ca 2)</t>
-  </si>
-  <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>02224367</t>
-  </si>
-  <si>
-    <t>Ngô Minh Hiếu</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>02227708</t>
-  </si>
-  <si>
-    <t>Phạm Việt Khải</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
-  </si>
-  <si>
-    <t>09/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 19:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca2</t>
-  </si>
-  <si>
-    <t>02022149</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Mạnh</t>
+    <t>Kiểm kê kho tháng 9.</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>11/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>11/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>02021645</t>
+  </si>
+  <si>
+    <t>Trịnh Xuân Tỉnh</t>
+  </si>
+  <si>
+    <t>02645269</t>
+  </si>
+  <si>
+    <t>Lê Thanh Toàn</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>10/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02619486</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>07/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>07/09/2026 18:30:00</t>
   </si>
   <si>
     <t>02243991</t>
@@ -217,88 +544,22 @@
     <t>lắp rack xưởng 3</t>
   </si>
   <si>
-    <t>17/09/2026 14:00:00</t>
-  </si>
-  <si>
     <t>17/09/2026 16:00:00</t>
   </si>
   <si>
-    <t>02220255</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Sơn</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>14/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>Lớn hơn KH</t>
-  </si>
-  <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
-  </si>
-  <si>
-    <t>09/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t>11/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t>10/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>10/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 16:30:00</t>
+    <t>17/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
   </si>
   <si>
     <t>02317843</t>
@@ -313,118 +574,139 @@
     <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
   </si>
   <si>
-    <t>02224288</t>
-  </si>
-  <si>
-    <t>Võ Văn Dương</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bonbin</t>
-  </si>
-  <si>
-    <t>21/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:00:00</t>
-  </si>
-  <si>
     <t>lắp rack bobin tại xưởng 3</t>
   </si>
   <si>
-    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất(ca2)</t>
-  </si>
-  <si>
     <t>02325374</t>
   </si>
   <si>
     <t>Trương Văn Tình</t>
   </si>
   <si>
+    <t>Tăng ca sản xuất ( Ca 2 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>16/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
     <t>Tăng ca lắp rack xưởng 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>07/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>07/09/2026 18:30:00</t>
-  </si>
-  <si>
-    <t>hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>Chờ cấp trên gian tiếp</t>
-  </si>
-  <si>
-    <t>17/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
-  </si>
-  <si>
-    <t>22/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bobin</t>
-  </si>
-  <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>Tăng ca sản xuất ( Ca 2 )</t>
-  </si>
-  <si>
-    <t>02516134</t>
-  </si>
-  <si>
-    <t>Ngô Xuân Nghĩa</t>
-  </si>
-  <si>
-    <t>thực hiện dự án cải tiến</t>
-  </si>
-  <si>
-    <t>hổ trợ nghiền</t>
-  </si>
-  <si>
-    <t>16/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
-  </si>
-  <si>
-    <t>Thực hiện dự án cải tiến</t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>08/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>08/09/2026 19:30:00</t>
+  </si>
+  <si>
+    <t>11/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>Tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>01921560</t>
+  </si>
+  <si>
+    <t>Trần Quang Hiệu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
+  </si>
+  <si>
+    <t>02021131</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Anh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>02020497</t>
+  </si>
+  <si>
+    <t>Vũ Nhân Tài</t>
+  </si>
+  <si>
+    <t>Tăng ca hổ trợ sản xuất (HC)</t>
+  </si>
+  <si>
+    <t>02645250</t>
+  </si>
+  <si>
+    <t>Trần Xuân Bắc</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền CA 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca thứ 7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
+  </si>
+  <si>
+    <t>17/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca 2</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca 1</t>
   </si>
   <si>
     <t>02325365</t>
@@ -436,475 +718,217 @@
     <t>tăng ca hỗ trợ sản xuất (ca 3)</t>
   </si>
   <si>
-    <t>02020965</t>
-  </si>
-  <si>
-    <t>Hà Xuân Tiến</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
-  </si>
-  <si>
     <t>02325310</t>
   </si>
   <si>
     <t>Nguyễn Công Hậu</t>
   </si>
   <si>
+    <t>tăng ca hỗ trợ sản xuất (ca3)</t>
+  </si>
+  <si>
     <t>tăng ca hỗ trợ sản xuất ( ca 1)</t>
   </si>
   <si>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>TĂNG CA SẢN XUẤT</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>chuẩn bị kiểm kê</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
+    <t>23/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>lắp đặt thiết bị</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chuẩn bị kiểm kê </t>
+  </si>
+  <si>
+    <t>24/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>02226596</t>
+  </si>
+  <si>
+    <t>Đoàn Văn Dương</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>02224358</t>
+  </si>
+  <si>
+    <t>Hoàng Trung Hiếu</t>
+  </si>
+  <si>
+    <t>ca1 tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>02228947</t>
+  </si>
+  <si>
+    <t>Phạm Lê Minh Tân</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca2 Tăng ca hỗ trợ Nghiền </t>
+  </si>
+  <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>Tăng Cường Sản Xuất</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>tăng ca đáp ứng tiến độ sản xuất</t>
+  </si>
+  <si>
+    <t>22/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>17/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
+    <t>16/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>tang ca cat ong nhua</t>
+  </si>
+  <si>
     <t>18/09/2026 12:30:00</t>
   </si>
   <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất (ca3)</t>
-  </si>
-  <si>
-    <t>02645269</t>
-  </si>
-  <si>
-    <t>Lê Thanh Toàn</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>02021742</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Dũng</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca 2</t>
-  </si>
-  <si>
-    <t>18/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca 1</t>
-  </si>
-  <si>
-    <t>16/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>02021131</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Anh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca sản xuất </t>
-  </si>
-  <si>
-    <t>02020752</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>15/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>02021645</t>
-  </si>
-  <si>
-    <t>Trịnh Xuân Tỉnh</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>02619486</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Huy</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>16/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02020497</t>
-  </si>
-  <si>
-    <t>Vũ Nhân Tài</t>
-  </si>
-  <si>
-    <t>Tăng ca hổ trợ sản xuất (HC)</t>
-  </si>
-  <si>
-    <t>11/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>10/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02645250</t>
-  </si>
-  <si>
-    <t>Trần Xuân Bắc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca thứ 7 </t>
-  </si>
-  <si>
-    <t>14/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ nghiền CA 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
-  </si>
-  <si>
-    <t>17/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>01920862</t>
-  </si>
-  <si>
-    <t>Nguyễn Khắc Kiên</t>
-  </si>
-  <si>
-    <t>TĂNG CA SẢN XUẤT</t>
-  </si>
-  <si>
-    <t>02021159</t>
-  </si>
-  <si>
-    <t>Trần Vương</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca 2</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất : ca 1</t>
-  </si>
-  <si>
-    <t>02020488</t>
-  </si>
-  <si>
-    <t>Lê Thanh Trúc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
-  </si>
-  <si>
-    <t>02411884</t>
-  </si>
-  <si>
-    <t>Phan Đình Lâm</t>
-  </si>
-  <si>
-    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
-  </si>
-  <si>
-    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Kiểm kê kho tháng 9.</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>02020390</t>
-  </si>
-  <si>
-    <t>Võ Thiên Tuế</t>
-  </si>
-  <si>
-    <t>Tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>02519007</t>
-  </si>
-  <si>
-    <t>Ninh Quang Trường</t>
-  </si>
-  <si>
-    <t>01921560</t>
-  </si>
-  <si>
-    <t>Trần Quang Hiệu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
-  </si>
-  <si>
-    <t>08/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>08/09/2026 19:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lắp rack xưởng 3 </t>
-  </si>
-  <si>
-    <t>02325295</t>
-  </si>
-  <si>
-    <t>Lưu Văn Đủ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền ca 3</t>
-  </si>
-  <si>
-    <t>03/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>03/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền ca 2</t>
-  </si>
-  <si>
-    <t>01921551</t>
-  </si>
-  <si>
-    <t>Trương Quang Nghĩa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hỗ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
-    <t>chuẩn bị kiểm kê</t>
-  </si>
-  <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>lắp đặt thiết bị</t>
-  </si>
-  <si>
-    <t>02222350</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Nguyên</t>
-  </si>
-  <si>
-    <t>Tăng cường sản xuất</t>
-  </si>
-  <si>
-    <t>02223526</t>
-  </si>
-  <si>
-    <t>Nguyễn Thiên Phú</t>
-  </si>
-  <si>
-    <t>02223605</t>
-  </si>
-  <si>
-    <t>Võ Minh Bắc</t>
-  </si>
-  <si>
-    <t>02226596</t>
-  </si>
-  <si>
-    <t>Đoàn Văn Dương</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>02224358</t>
-  </si>
-  <si>
-    <t>Hoàng Trung Hiếu</t>
-  </si>
-  <si>
-    <t>ca1 tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca2 Tăng ca hỗ trợ Nghiền </t>
-  </si>
-  <si>
-    <t>02228947</t>
-  </si>
-  <si>
-    <t>Phạm Lê Minh Tân</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>02243654</t>
-  </si>
-  <si>
-    <t>Lưu Văn Giang</t>
-  </si>
-  <si>
-    <t>Tăng Cường Sản Xuất</t>
-  </si>
-  <si>
-    <t>02622116</t>
-  </si>
-  <si>
-    <t>Trịnh Nhựt Khánh</t>
-  </si>
-  <si>
-    <t>02644057</t>
-  </si>
-  <si>
-    <t>Phạm Văn Công</t>
-  </si>
-  <si>
-    <t>tăng ca đáp ứng tiến độ sản xuất</t>
-  </si>
-  <si>
-    <t>22/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>tang ca cat ong nhua</t>
-  </si>
-  <si>
     <t>tang ca van hanh may nghien</t>
   </si>
   <si>
     <t xml:space="preserve">tang ca cat ong nhua </t>
   </si>
   <si>
-    <t>22/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 15:30:00</t>
-  </si>
-  <si>
     <t>21/09/2026 15:30:00</t>
   </si>
   <si>
-    <t>21/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 22:00:00</t>
-  </si>
-  <si>
     <t>tăng ca cǎt ông nhua</t>
   </si>
   <si>
     <t>14/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 15:30:00</t>
   </si>
 </sst>
 </file>
@@ -1418,7 +1442,7 @@
         <v>25</v>
       </c>
       <c r="J3" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>24</v>
@@ -1460,19 +1484,19 @@
         <v>23</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="8">
+        <v>90</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="8">
-        <v>480</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="L4" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
@@ -1499,7 +1523,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>22</v>
@@ -1508,19 +1532,19 @@
         <v>23</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J5" s="8">
         <v>480</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M5" s="8">
         <v>0</v>
@@ -1535,10 +1559,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>19</v>
@@ -1547,7 +1571,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>22</v>
@@ -1556,19 +1580,19 @@
         <v>23</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J6" s="8">
         <v>480</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M6" s="8">
         <v>0</v>
@@ -1583,10 +1607,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>19</v>
@@ -1595,7 +1619,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -1604,19 +1628,19 @@
         <v>23</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J7" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" s="8">
         <v>0</v>
@@ -1631,10 +1655,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>19</v>
@@ -1652,19 +1676,19 @@
         <v>23</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J8" s="8">
         <v>480</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M8" s="8">
         <v>0</v>
@@ -1679,20 +1703,20 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="F9" s="7" t="s">
         <v>22</v>
       </c>
@@ -1700,19 +1724,19 @@
         <v>23</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" s="8">
         <v>480</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M9" s="8">
         <v>0</v>
@@ -1727,10 +1751,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>19</v>
@@ -1739,7 +1763,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
@@ -1748,19 +1772,19 @@
         <v>23</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="J10" s="8">
         <v>480</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="M10" s="8">
         <v>0</v>
@@ -1775,10 +1799,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>19</v>
@@ -1787,7 +1811,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>22</v>
@@ -1796,19 +1820,19 @@
         <v>23</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J11" s="8">
         <v>480</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M11" s="8">
         <v>0</v>
@@ -1823,10 +1847,10 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>19</v>
@@ -1835,7 +1859,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>22</v>
@@ -1844,26 +1868,26 @@
         <v>23</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="J12" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="M12" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N12" s="7"/>
       <c r="O12" s="8" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="P12" s="8" t="s">
         <v>27</v>
@@ -1871,10 +1895,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>19</v>
@@ -1883,7 +1907,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>22</v>
@@ -1892,19 +1916,19 @@
         <v>23</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="J13" s="8">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="M13" s="8">
         <v>0</v>
@@ -1919,10 +1943,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>19</v>
@@ -1931,7 +1955,7 @@
         <v>20</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
@@ -1940,19 +1964,19 @@
         <v>23</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J14" s="8">
         <v>480</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M14" s="8">
         <v>0</v>
@@ -1967,10 +1991,10 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>19</v>
@@ -1979,7 +2003,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>22</v>
@@ -1988,19 +2012,19 @@
         <v>23</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J15" s="8">
         <v>480</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M15" s="8">
         <v>0</v>
@@ -2015,10 +2039,10 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>19</v>
@@ -2027,7 +2051,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>22</v>
@@ -2036,19 +2060,19 @@
         <v>23</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="J16" s="8">
         <v>480</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="M16" s="8">
         <v>0</v>
@@ -2063,10 +2087,10 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>19</v>
@@ -2075,7 +2099,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>22</v>
@@ -2084,19 +2108,19 @@
         <v>23</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="J17" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="M17" s="8">
         <v>0</v>
@@ -2111,10 +2135,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>19</v>
@@ -2123,7 +2147,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>22</v>
@@ -2132,26 +2156,26 @@
         <v>23</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="J18" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="M18" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N18" s="7"/>
       <c r="O18" s="8" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="P18" s="8" t="s">
         <v>27</v>
@@ -2159,10 +2183,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>19</v>
@@ -2171,7 +2195,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>22</v>
@@ -2180,19 +2204,19 @@
         <v>23</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J19" s="8">
         <v>480</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M19" s="8">
         <v>0</v>
@@ -2207,10 +2231,10 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>19</v>
@@ -2219,7 +2243,7 @@
         <v>20</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>22</v>
@@ -2228,26 +2252,26 @@
         <v>23</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J20" s="8">
         <v>120</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M20" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N20" s="7"/>
       <c r="O20" s="8" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="P20" s="8" t="s">
         <v>27</v>
@@ -2255,10 +2279,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>19</v>
@@ -2267,28 +2291,28 @@
         <v>20</v>
       </c>
       <c r="E21" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="J21" s="8">
         <v>480</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M21" s="8">
         <v>0</v>
@@ -2303,10 +2327,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>19</v>
@@ -2315,7 +2339,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>22</v>
@@ -2324,19 +2348,19 @@
         <v>23</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="J22" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="M22" s="8">
         <v>0</v>
@@ -2351,10 +2375,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>19</v>
@@ -2363,7 +2387,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>22</v>
@@ -2372,19 +2396,19 @@
         <v>23</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J23" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M23" s="8">
         <v>0</v>
@@ -2399,10 +2423,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>19</v>
@@ -2411,28 +2435,28 @@
         <v>20</v>
       </c>
       <c r="E24" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="J24" s="8">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="M24" s="8">
         <v>0</v>
@@ -2447,40 +2471,40 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>90</v>
-      </c>
       <c r="I25" s="8" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="J25" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="M25" s="8">
         <v>0</v>
@@ -2495,10 +2519,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>19</v>
@@ -2507,7 +2531,7 @@
         <v>20</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>22</v>
@@ -2516,19 +2540,19 @@
         <v>23</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="J26" s="8">
         <v>480</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="M26" s="8">
         <v>0</v>
@@ -2543,10 +2567,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>19</v>
@@ -2555,7 +2579,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>22</v>
@@ -2564,19 +2588,19 @@
         <v>23</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="J27" s="8">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="M27" s="8">
         <v>0</v>
@@ -2591,10 +2615,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>19</v>
@@ -2603,7 +2627,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>22</v>
@@ -2612,19 +2636,19 @@
         <v>23</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="J28" s="8">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="M28" s="8">
         <v>0</v>
@@ -2639,19 +2663,19 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>22</v>
@@ -2660,26 +2684,26 @@
         <v>23</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="J29" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="M29" s="8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N29" s="7"/>
       <c r="O29" s="8" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="P29" s="8" t="s">
         <v>27</v>
@@ -2687,10 +2711,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>19</v>
@@ -2699,7 +2723,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>22</v>
@@ -2708,19 +2732,19 @@
         <v>23</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J30" s="4">
         <v>480</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M30" s="4">
         <v>0</v>
@@ -2735,10 +2759,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>19</v>
@@ -2747,7 +2771,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>22</v>
@@ -2756,19 +2780,19 @@
         <v>23</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="J31" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="M31" s="4">
         <v>0</v>
@@ -2783,19 +2807,19 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>22</v>
@@ -2804,19 +2828,19 @@
         <v>23</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="J32" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="M32" s="4">
         <v>0</v>
@@ -2831,10 +2855,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>19</v>
@@ -2843,7 +2867,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>22</v>
@@ -2852,19 +2876,19 @@
         <v>23</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="J33" s="4">
         <v>480</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="M33" s="4">
         <v>0</v>
@@ -2879,19 +2903,19 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>22</v>
@@ -2900,19 +2924,19 @@
         <v>23</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="J34" s="4">
         <v>480</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="M34" s="4">
         <v>0</v>
@@ -2927,10 +2951,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>19</v>
@@ -2939,7 +2963,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>22</v>
@@ -2948,19 +2972,19 @@
         <v>23</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J35" s="4">
         <v>480</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M35" s="4">
         <v>0</v>
@@ -2975,10 +2999,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
@@ -2987,7 +3011,7 @@
         <v>20</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>22</v>
@@ -2996,26 +3020,26 @@
         <v>23</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="J36" s="4">
         <v>120</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="M36" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="4" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="P36" s="4" t="s">
         <v>27</v>
@@ -3023,10 +3047,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>19</v>
@@ -3035,7 +3059,7 @@
         <v>20</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>22</v>
@@ -3044,19 +3068,19 @@
         <v>23</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="J37" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="M37" s="4">
         <v>0</v>
@@ -3071,19 +3095,19 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>22</v>
@@ -3092,19 +3116,19 @@
         <v>23</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="J38" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="M38" s="4">
         <v>0</v>
@@ -3114,15 +3138,15 @@
         <v>26</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
@@ -3131,7 +3155,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>22</v>
@@ -3146,7 +3170,7 @@
         <v>119</v>
       </c>
       <c r="J39" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>118</v>
@@ -3167,10 +3191,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>19</v>
@@ -3194,7 +3218,7 @@
         <v>122</v>
       </c>
       <c r="J40" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>121</v>
@@ -3210,15 +3234,15 @@
         <v>26</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
@@ -3227,7 +3251,7 @@
         <v>20</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>22</v>
@@ -3236,19 +3260,19 @@
         <v>23</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="J41" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="M41" s="4">
         <v>0</v>
@@ -3263,10 +3287,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>19</v>
@@ -3275,7 +3299,7 @@
         <v>20</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>22</v>
@@ -3284,19 +3308,19 @@
         <v>23</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="J42" s="4">
         <v>90</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="M42" s="4">
         <v>0</v>
@@ -3311,10 +3335,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
@@ -3323,7 +3347,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>22</v>
@@ -3332,19 +3356,19 @@
         <v>23</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="J43" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="M43" s="4">
         <v>0</v>
@@ -3359,10 +3383,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
@@ -3371,7 +3395,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>22</v>
@@ -3380,19 +3404,19 @@
         <v>23</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="J44" s="4">
         <v>480</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="M44" s="4">
         <v>0</v>
@@ -3407,10 +3431,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>19</v>
@@ -3419,7 +3443,7 @@
         <v>20</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>22</v>
@@ -3428,19 +3452,19 @@
         <v>23</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="J45" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="M45" s="4">
         <v>0</v>
@@ -3455,10 +3479,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>19</v>
@@ -3467,7 +3491,7 @@
         <v>20</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>22</v>
@@ -3476,19 +3500,19 @@
         <v>23</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="J46" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="M46" s="4">
         <v>0</v>
@@ -3503,10 +3527,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>19</v>
@@ -3515,7 +3539,7 @@
         <v>20</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>22</v>
@@ -3524,19 +3548,19 @@
         <v>23</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="J47" s="4">
         <v>480</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="M47" s="4">
         <v>0</v>
@@ -3551,10 +3575,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>19</v>
@@ -3563,7 +3587,7 @@
         <v>20</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>22</v>
@@ -3572,19 +3596,19 @@
         <v>23</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="J48" s="4">
         <v>90</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="M48" s="4">
         <v>0</v>
@@ -3599,10 +3623,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>19</v>
@@ -3611,7 +3635,7 @@
         <v>20</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>22</v>
@@ -3620,19 +3644,19 @@
         <v>23</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>67</v>
+        <v>140</v>
       </c>
       <c r="J49" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>67</v>
+        <v>140</v>
       </c>
       <c r="M49" s="4">
         <v>0</v>
@@ -3647,10 +3671,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>19</v>
@@ -3659,7 +3683,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>22</v>
@@ -3668,19 +3692,19 @@
         <v>23</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J50" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M50" s="4">
         <v>0</v>
@@ -3695,10 +3719,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>19</v>
@@ -3707,7 +3731,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>22</v>
@@ -3716,19 +3740,19 @@
         <v>23</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="J51" s="4">
         <v>480</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="M51" s="4">
         <v>0</v>
@@ -3743,10 +3767,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>19</v>
@@ -3755,7 +3779,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>22</v>
@@ -3764,19 +3788,19 @@
         <v>23</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="J52" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="M52" s="4">
         <v>0</v>
@@ -3791,10 +3815,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>19</v>
@@ -3803,7 +3827,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>22</v>
@@ -3812,19 +3836,19 @@
         <v>23</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>145</v>
+        <v>96</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="J53" s="4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>145</v>
+        <v>96</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="M53" s="4">
         <v>0</v>
@@ -3839,10 +3863,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>19</v>
@@ -3851,7 +3875,7 @@
         <v>20</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>22</v>
@@ -3860,19 +3884,19 @@
         <v>23</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="J54" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="M54" s="4">
         <v>0</v>
@@ -3887,10 +3911,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>19</v>
@@ -3899,7 +3923,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>22</v>
@@ -3908,19 +3932,19 @@
         <v>23</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
       <c r="J55" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
       <c r="M55" s="4">
         <v>0</v>
@@ -3935,10 +3959,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>19</v>
@@ -3947,7 +3971,7 @@
         <v>20</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>22</v>
@@ -3956,19 +3980,19 @@
         <v>23</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>24</v>
+        <v>154</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="J56" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>24</v>
+        <v>154</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="M56" s="4">
         <v>0</v>
@@ -3983,10 +4007,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>19</v>
@@ -3995,7 +4019,7 @@
         <v>20</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>22</v>
@@ -4004,19 +4028,19 @@
         <v>23</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="J57" s="4">
         <v>480</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="M57" s="4">
         <v>0</v>
@@ -4031,10 +4055,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>150</v>
+        <v>81</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>19</v>
@@ -4043,7 +4067,7 @@
         <v>20</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>22</v>
@@ -4052,19 +4076,19 @@
         <v>23</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I58" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="J58" s="4">
+        <v>120</v>
+      </c>
+      <c r="K58" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="J58" s="4">
-        <v>90</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="L58" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M58" s="4">
         <v>0</v>
@@ -4079,10 +4103,10 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>19</v>
@@ -4091,7 +4115,7 @@
         <v>20</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>22</v>
@@ -4100,19 +4124,19 @@
         <v>23</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="J59" s="4">
         <v>480</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="M59" s="4">
         <v>0</v>
@@ -4127,10 +4151,10 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>19</v>
@@ -4139,7 +4163,7 @@
         <v>20</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>22</v>
@@ -4148,19 +4172,19 @@
         <v>23</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="J60" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="M60" s="4">
         <v>0</v>
@@ -4175,10 +4199,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>19</v>
@@ -4187,7 +4211,7 @@
         <v>20</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>22</v>
@@ -4196,19 +4220,19 @@
         <v>23</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="J61" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="M61" s="4">
         <v>0</v>
@@ -4223,10 +4247,10 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>19</v>
@@ -4235,7 +4259,7 @@
         <v>20</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>22</v>
@@ -4244,19 +4268,19 @@
         <v>23</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="J62" s="4">
         <v>480</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="M62" s="4">
         <v>0</v>
@@ -4271,10 +4295,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>19</v>
@@ -4283,7 +4307,7 @@
         <v>20</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>22</v>
@@ -4292,19 +4316,19 @@
         <v>23</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="J63" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="M63" s="4">
         <v>0</v>
@@ -4319,19 +4343,19 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>22</v>
@@ -4340,19 +4364,19 @@
         <v>23</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="J64" s="4">
         <v>480</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="M64" s="4">
         <v>0</v>
@@ -4367,10 +4391,10 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>19</v>
@@ -4379,7 +4403,7 @@
         <v>20</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>22</v>
@@ -4388,19 +4412,19 @@
         <v>23</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J65" s="4">
         <v>120</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="M65" s="4">
         <v>0</v>
@@ -4415,19 +4439,19 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>22</v>
@@ -4436,19 +4460,19 @@
         <v>23</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="J66" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="M66" s="4">
         <v>0</v>
@@ -4463,10 +4487,10 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>19</v>
@@ -4484,19 +4508,19 @@
         <v>23</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>24</v>
+        <v>176</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>25</v>
+        <v>177</v>
       </c>
       <c r="J67" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>24</v>
+        <v>176</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>25</v>
+        <v>177</v>
       </c>
       <c r="M67" s="4">
         <v>0</v>
@@ -4511,10 +4535,10 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>19</v>
@@ -4523,7 +4547,7 @@
         <v>20</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>22</v>
@@ -4532,19 +4556,19 @@
         <v>23</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="J68" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="M68" s="4">
         <v>0</v>
@@ -4559,10 +4583,10 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>19</v>
@@ -4571,7 +4595,7 @@
         <v>20</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>22</v>
@@ -4580,19 +4604,19 @@
         <v>23</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J69" s="4">
         <v>480</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="M69" s="4">
         <v>0</v>
@@ -4607,10 +4631,10 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>19</v>
@@ -4619,7 +4643,7 @@
         <v>20</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>22</v>
@@ -4628,19 +4652,19 @@
         <v>23</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="J70" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="M70" s="4">
         <v>0</v>
@@ -4655,19 +4679,19 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>22</v>
@@ -4676,19 +4700,19 @@
         <v>23</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="J71" s="4">
         <v>480</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="M71" s="4">
         <v>0</v>
@@ -4703,19 +4727,19 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>22</v>
@@ -4724,19 +4748,19 @@
         <v>23</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>178</v>
+        <v>51</v>
       </c>
       <c r="J72" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>178</v>
+        <v>51</v>
       </c>
       <c r="M72" s="4">
         <v>0</v>
@@ -4751,10 +4775,10 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>19</v>
@@ -4763,7 +4787,7 @@
         <v>20</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>22</v>
@@ -4772,19 +4796,19 @@
         <v>23</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>179</v>
+        <v>39</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="J73" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>179</v>
+        <v>39</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="M73" s="4">
         <v>0</v>
@@ -4799,10 +4823,10 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>19</v>
@@ -4811,7 +4835,7 @@
         <v>20</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>22</v>
@@ -4820,19 +4844,19 @@
         <v>23</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="J74" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="M74" s="4">
         <v>0</v>
@@ -4847,10 +4871,10 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>19</v>
@@ -4859,7 +4883,7 @@
         <v>20</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>22</v>
@@ -4868,19 +4892,19 @@
         <v>23</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>24</v>
+        <v>190</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>25</v>
+        <v>191</v>
       </c>
       <c r="J75" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>24</v>
+        <v>190</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>25</v>
+        <v>191</v>
       </c>
       <c r="M75" s="4">
         <v>0</v>
@@ -4895,10 +4919,10 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>19</v>
@@ -4907,7 +4931,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>22</v>
@@ -4916,19 +4940,19 @@
         <v>23</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>185</v>
+        <v>45</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>186</v>
+        <v>34</v>
       </c>
       <c r="J76" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>185</v>
+        <v>45</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>186</v>
+        <v>34</v>
       </c>
       <c r="M76" s="4">
         <v>0</v>
@@ -4943,10 +4967,10 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>19</v>
@@ -4955,7 +4979,7 @@
         <v>20</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>22</v>
@@ -4964,19 +4988,19 @@
         <v>23</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="J77" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="M77" s="4">
         <v>0</v>
@@ -4991,10 +5015,10 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>19</v>
@@ -5003,7 +5027,7 @@
         <v>20</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>22</v>
@@ -5012,19 +5036,19 @@
         <v>23</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="J78" s="4">
         <v>90</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="M78" s="4">
         <v>0</v>
@@ -5039,10 +5063,10 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>19</v>
@@ -5051,7 +5075,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>22</v>
@@ -5060,19 +5084,19 @@
         <v>23</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="J79" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="M79" s="4">
         <v>0</v>
@@ -5087,10 +5111,10 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>19</v>
@@ -5099,7 +5123,7 @@
         <v>20</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>22</v>
@@ -5108,19 +5132,19 @@
         <v>23</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>189</v>
+        <v>35</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="J80" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>189</v>
+        <v>35</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="M80" s="4">
         <v>0</v>
@@ -5135,10 +5159,10 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>19</v>
@@ -5147,7 +5171,7 @@
         <v>20</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>22</v>
@@ -5156,26 +5180,26 @@
         <v>23</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="J81" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="M81" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N81" s="3"/>
       <c r="O81" s="4" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="P81" s="4" t="s">
         <v>27</v>
@@ -5183,10 +5207,10 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>19</v>
@@ -5195,7 +5219,7 @@
         <v>20</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>22</v>
@@ -5204,19 +5228,19 @@
         <v>23</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="J82" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="M82" s="4">
         <v>0</v>
@@ -5231,10 +5255,10 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>19</v>
@@ -5243,7 +5267,7 @@
         <v>20</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>22</v>
@@ -5252,19 +5276,19 @@
         <v>23</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="J83" s="4">
         <v>480</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="M83" s="4">
         <v>0</v>
@@ -5279,10 +5303,10 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>19</v>
@@ -5291,7 +5315,7 @@
         <v>20</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>22</v>
@@ -5300,19 +5324,19 @@
         <v>23</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="J84" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="M84" s="4">
         <v>0</v>
@@ -5327,10 +5351,10 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>19</v>
@@ -5339,7 +5363,7 @@
         <v>20</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>22</v>
@@ -5348,19 +5372,19 @@
         <v>23</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="J85" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="M85" s="4">
         <v>0</v>
@@ -5375,40 +5399,40 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="I86" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C86" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="J86" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>36</v>
+        <v>198</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>37</v>
+        <v>199</v>
       </c>
       <c r="M86" s="4">
         <v>0</v>
@@ -5423,10 +5447,10 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>19</v>
@@ -5435,7 +5459,7 @@
         <v>20</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>22</v>
@@ -5444,19 +5468,19 @@
         <v>23</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>92</v>
+        <v>200</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>93</v>
+        <v>201</v>
       </c>
       <c r="J87" s="4">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>92</v>
+        <v>200</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>93</v>
+        <v>201</v>
       </c>
       <c r="M87" s="4">
         <v>0</v>
@@ -5471,40 +5495,40 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I88" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I88" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="J88" s="4">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>59</v>
+        <v>202</v>
       </c>
       <c r="M88" s="4">
         <v>0</v>
@@ -5519,10 +5543,10 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>19</v>
@@ -5531,7 +5555,7 @@
         <v>20</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>206</v>
+        <v>168</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>22</v>
@@ -5540,19 +5564,19 @@
         <v>23</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="J89" s="4">
         <v>90</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="M89" s="4">
         <v>0</v>
@@ -5567,40 +5591,40 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H90" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="I90" s="4" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="J90" s="4">
         <v>90</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="M90" s="4">
         <v>0</v>
@@ -5615,10 +5639,10 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>19</v>
@@ -5627,7 +5651,7 @@
         <v>20</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>22</v>
@@ -5636,19 +5660,19 @@
         <v>23</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>212</v>
+        <v>34</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>213</v>
+        <v>35</v>
       </c>
       <c r="J91" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>212</v>
+        <v>34</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>213</v>
+        <v>35</v>
       </c>
       <c r="M91" s="4">
         <v>0</v>
@@ -5663,10 +5687,10 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>19</v>
@@ -5675,7 +5699,7 @@
         <v>20</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>22</v>
@@ -5684,19 +5708,19 @@
         <v>23</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J92" s="4">
         <v>480</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M92" s="4">
         <v>0</v>
@@ -5711,10 +5735,10 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>19</v>
@@ -5723,7 +5747,7 @@
         <v>20</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>216</v>
+        <v>63</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>22</v>
@@ -5732,19 +5756,19 @@
         <v>23</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J93" s="4">
         <v>480</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="M93" s="4">
         <v>0</v>
@@ -5759,10 +5783,10 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>19</v>
@@ -5771,7 +5795,7 @@
         <v>20</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>22</v>
@@ -5780,19 +5804,19 @@
         <v>23</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="J94" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="M94" s="4">
         <v>0</v>
@@ -5807,10 +5831,10 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>19</v>
@@ -5819,7 +5843,7 @@
         <v>20</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>35</v>
+        <v>211</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>22</v>
@@ -5828,26 +5852,26 @@
         <v>23</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="J95" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="M95" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N95" s="3"/>
       <c r="O95" s="4" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="P95" s="4" t="s">
         <v>27</v>
@@ -5855,10 +5879,10 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>19</v>
@@ -5867,7 +5891,7 @@
         <v>20</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>22</v>
@@ -5876,19 +5900,19 @@
         <v>23</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>34</v>
+        <v>157</v>
       </c>
       <c r="J96" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>34</v>
+        <v>157</v>
       </c>
       <c r="M96" s="4">
         <v>0</v>
@@ -5903,10 +5927,10 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>19</v>
@@ -5915,7 +5939,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>22</v>
@@ -5924,19 +5948,19 @@
         <v>23</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J97" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="M97" s="4">
         <v>0</v>
@@ -5951,10 +5975,10 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>219</v>
+        <v>75</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>19</v>
@@ -5963,7 +5987,7 @@
         <v>20</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>222</v>
+        <v>63</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>22</v>
@@ -5972,26 +5996,26 @@
         <v>23</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="J98" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M98" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N98" s="3"/>
       <c r="O98" s="4" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="P98" s="4" t="s">
         <v>27</v>
@@ -5999,10 +6023,10 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>19</v>
@@ -6011,7 +6035,7 @@
         <v>20</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>22</v>
@@ -6020,19 +6044,19 @@
         <v>23</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>207</v>
+        <v>34</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>208</v>
+        <v>35</v>
       </c>
       <c r="J99" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>207</v>
+        <v>34</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>208</v>
+        <v>35</v>
       </c>
       <c r="M99" s="4">
         <v>0</v>
@@ -6047,10 +6071,10 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>19</v>
@@ -6059,7 +6083,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>22</v>
@@ -6068,19 +6092,19 @@
         <v>23</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="J100" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="M100" s="4">
         <v>0</v>
@@ -6095,10 +6119,10 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>19</v>
@@ -6107,7 +6131,7 @@
         <v>20</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>22</v>
@@ -6116,19 +6140,19 @@
         <v>23</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="J101" s="4">
         <v>90</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="M101" s="4">
         <v>0</v>
@@ -6155,7 +6179,7 @@
         <v>20</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>123</v>
+        <v>222</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>22</v>
@@ -6164,19 +6188,19 @@
         <v>23</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="J102" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="M102" s="4">
         <v>0</v>
@@ -6191,10 +6215,10 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>19</v>
@@ -6203,7 +6227,7 @@
         <v>20</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>22</v>
@@ -6212,19 +6236,19 @@
         <v>23</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>224</v>
+        <v>35</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>225</v>
+        <v>88</v>
       </c>
       <c r="J103" s="4">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>224</v>
+        <v>35</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>225</v>
+        <v>88</v>
       </c>
       <c r="M103" s="4">
         <v>0</v>
@@ -6239,10 +6263,10 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>68</v>
+        <v>219</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>19</v>
@@ -6251,7 +6275,7 @@
         <v>20</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>54</v>
+        <v>223</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>22</v>
@@ -6260,19 +6284,19 @@
         <v>23</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>31</v>
+        <v>194</v>
       </c>
       <c r="J104" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>31</v>
+        <v>194</v>
       </c>
       <c r="M104" s="4">
         <v>0</v>
@@ -6287,10 +6311,10 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>68</v>
+        <v>219</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>19</v>
@@ -6299,7 +6323,7 @@
         <v>20</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>54</v>
+        <v>223</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>22</v>
@@ -6308,19 +6332,19 @@
         <v>23</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>36</v>
+        <v>224</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>37</v>
+        <v>225</v>
       </c>
       <c r="J105" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>36</v>
+        <v>224</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>37</v>
+        <v>225</v>
       </c>
       <c r="M105" s="4">
         <v>0</v>
@@ -6335,10 +6359,10 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>68</v>
+        <v>226</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>69</v>
+        <v>227</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>19</v>
@@ -6347,7 +6371,7 @@
         <v>20</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>70</v>
+        <v>228</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>22</v>
@@ -6356,19 +6380,19 @@
         <v>23</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="J106" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="M106" s="4">
         <v>0</v>
@@ -6383,10 +6407,10 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>68</v>
+        <v>226</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>69</v>
+        <v>227</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>19</v>
@@ -6395,7 +6419,7 @@
         <v>20</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>22</v>
@@ -6404,19 +6428,19 @@
         <v>23</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="J107" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="M107" s="4">
         <v>0</v>
@@ -6431,10 +6455,10 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>68</v>
+        <v>230</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>69</v>
+        <v>231</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>19</v>
@@ -6443,7 +6467,7 @@
         <v>20</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>70</v>
+        <v>232</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>22</v>
@@ -6452,19 +6476,19 @@
         <v>23</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="J108" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="M108" s="4">
         <v>0</v>
@@ -6479,10 +6503,10 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>19</v>
@@ -6491,7 +6515,7 @@
         <v>20</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>22</v>
@@ -6500,19 +6524,19 @@
         <v>23</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="J109" s="4">
         <v>480</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="M109" s="4">
         <v>0</v>
@@ -6527,10 +6551,10 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>19</v>
@@ -6539,7 +6563,7 @@
         <v>20</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>22</v>
@@ -6548,19 +6572,19 @@
         <v>23</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>233</v>
+        <v>74</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>234</v>
+        <v>39</v>
       </c>
       <c r="J110" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>233</v>
+        <v>74</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>234</v>
+        <v>39</v>
       </c>
       <c r="M110" s="4">
         <v>0</v>
@@ -6575,10 +6599,10 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>19</v>
@@ -6587,7 +6611,7 @@
         <v>20</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>22</v>
@@ -6596,19 +6620,19 @@
         <v>23</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J111" s="4">
         <v>480</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M111" s="4">
         <v>0</v>
@@ -6623,10 +6647,10 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>19</v>
@@ -6635,7 +6659,7 @@
         <v>20</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>22</v>
@@ -6644,7 +6668,7 @@
         <v>23</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>34</v>
@@ -6653,7 +6677,7 @@
         <v>480</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="L112" s="4" t="s">
         <v>34</v>
@@ -6671,40 +6695,40 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="J113" s="4">
         <v>480</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="M113" s="4">
         <v>0</v>
@@ -6719,40 +6743,40 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>242</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>207</v>
+        <v>45</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>208</v>
+        <v>34</v>
       </c>
       <c r="J114" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>207</v>
+        <v>45</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>208</v>
+        <v>34</v>
       </c>
       <c r="M114" s="4">
         <v>0</v>
@@ -6776,31 +6800,31 @@
         <v>19</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>245</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="I115" s="4" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="J115" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="M115" s="4">
         <v>0</v>
@@ -6815,40 +6839,40 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>246</v>
+        <v>50</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>247</v>
+        <v>51</v>
       </c>
       <c r="J116" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>246</v>
+        <v>50</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>247</v>
+        <v>51</v>
       </c>
       <c r="M116" s="4">
         <v>0</v>
@@ -6863,40 +6887,40 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E117" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="I117" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="F117" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I117" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="J117" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>75</v>
+        <v>247</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="M117" s="4">
         <v>0</v>
@@ -6920,31 +6944,31 @@
         <v>19</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J118" s="4">
         <v>480</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="M118" s="4">
         <v>0</v>
@@ -6959,40 +6983,40 @@
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B119" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E119" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C119" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E119" s="3" t="s">
+      <c r="F119" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H119" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="F119" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="I119" s="4" t="s">
-        <v>37</v>
+        <v>252</v>
       </c>
       <c r="J119" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>36</v>
+        <v>251</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>37</v>
+        <v>252</v>
       </c>
       <c r="M119" s="4">
         <v>0</v>
@@ -7007,40 +7031,40 @@
     </row>
     <row r="120">
       <c r="A120" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I120" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J120" s="4">
         <v>480</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="M120" s="4">
         <v>0</v>
@@ -7055,40 +7079,40 @@
     </row>
     <row r="121">
       <c r="A121" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J121" s="4">
         <v>480</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M121" s="4">
         <v>0</v>
@@ -7103,40 +7127,40 @@
     </row>
     <row r="122">
       <c r="A122" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I122" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J122" s="4">
         <v>480</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M122" s="4">
         <v>0</v>
@@ -7151,40 +7175,40 @@
     </row>
     <row r="123">
       <c r="A123" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I123" s="4" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J123" s="4">
         <v>480</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="M123" s="4">
         <v>0</v>
@@ -7199,40 +7223,40 @@
     </row>
     <row r="124">
       <c r="A124" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>245</v>
+        <v>111</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="I124" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J124" s="4">
         <v>480</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M124" s="4">
         <v>0</v>
@@ -7247,40 +7271,40 @@
     </row>
     <row r="125">
       <c r="A125" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="J125" s="4">
         <v>120</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="M125" s="4">
         <v>0</v>
@@ -7295,40 +7319,40 @@
     </row>
     <row r="126">
       <c r="A126" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I126" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J126" s="4">
         <v>480</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M126" s="4">
         <v>0</v>
@@ -7343,40 +7367,40 @@
     </row>
     <row r="127">
       <c r="A127" s="3" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="J127" s="4">
         <v>480</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="M127" s="4">
         <v>0</v>
@@ -7391,40 +7415,40 @@
     </row>
     <row r="128">
       <c r="A128" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I128" s="4" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="J128" s="4">
         <v>480</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="M128" s="4">
         <v>0</v>
@@ -7439,40 +7463,40 @@
     </row>
     <row r="129">
       <c r="A129" s="3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>54</v>
+        <v>269</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I129" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J129" s="4">
         <v>480</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M129" s="4">
         <v>0</v>
@@ -7487,40 +7511,40 @@
     </row>
     <row r="130">
       <c r="A130" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>268</v>
+        <v>63</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I130" s="4" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="J130" s="4">
         <v>480</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="M130" s="4">
         <v>0</v>
@@ -7535,40 +7559,40 @@
     </row>
     <row r="131">
       <c r="A131" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I131" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J131" s="4">
         <v>480</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M131" s="4">
         <v>0</v>
@@ -7583,40 +7607,40 @@
     </row>
     <row r="132">
       <c r="A132" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="I132" s="4" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="J132" s="4">
         <v>480</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="M132" s="4">
         <v>0</v>
@@ -7631,40 +7655,40 @@
     </row>
     <row r="133">
       <c r="A133" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H133" s="4" t="s">
-        <v>33</v>
+        <v>224</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>34</v>
+        <v>225</v>
       </c>
       <c r="J133" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>33</v>
+        <v>224</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>34</v>
+        <v>225</v>
       </c>
       <c r="M133" s="4">
         <v>0</v>
@@ -7679,40 +7703,40 @@
     </row>
     <row r="134">
       <c r="A134" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="J134" s="4">
         <v>90</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="M134" s="4">
         <v>0</v>
@@ -7727,40 +7751,40 @@
     </row>
     <row r="135">
       <c r="A135" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>185</v>
+        <v>276</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>186</v>
+        <v>42</v>
       </c>
       <c r="J135" s="4">
         <v>90</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>185</v>
+        <v>276</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>186</v>
+        <v>42</v>
       </c>
       <c r="M135" s="4">
         <v>0</v>
@@ -7775,40 +7799,40 @@
     </row>
     <row r="136">
       <c r="A136" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="I136" s="4" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="J136" s="4">
         <v>90</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="M136" s="4">
         <v>0</v>
@@ -7823,40 +7847,40 @@
     </row>
     <row r="137">
       <c r="A137" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>274</v>
+        <v>198</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>121</v>
+        <v>199</v>
       </c>
       <c r="J137" s="4">
         <v>90</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>274</v>
+        <v>198</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>121</v>
+        <v>199</v>
       </c>
       <c r="M137" s="4">
         <v>0</v>
@@ -7871,40 +7895,40 @@
     </row>
     <row r="138">
       <c r="A138" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>275</v>
+        <v>193</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="J138" s="4">
         <v>90</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>275</v>
+        <v>193</v>
       </c>
       <c r="L138" s="4" t="s">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="M138" s="4">
         <v>0</v>
@@ -7919,40 +7943,40 @@
     </row>
     <row r="139">
       <c r="A139" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="J139" s="4">
         <v>90</v>
       </c>
       <c r="K139" s="4" t="s">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="L139" s="4" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="M139" s="4">
         <v>0</v>
@@ -7967,40 +7991,40 @@
     </row>
     <row r="140">
       <c r="A140" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="J140" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K140" s="4" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="L140" s="4" t="s">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="M140" s="4">
         <v>0</v>
@@ -8015,40 +8039,40 @@
     </row>
     <row r="141">
       <c r="A141" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="I141" s="4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J141" s="4">
         <v>480</v>
       </c>
       <c r="K141" s="4" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="M141" s="4">
         <v>0</v>
@@ -8063,40 +8087,40 @@
     </row>
     <row r="142">
       <c r="A142" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>33</v>
+        <v>278</v>
       </c>
       <c r="I142" s="4" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J142" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K142" s="4" t="s">
-        <v>33</v>
+        <v>278</v>
       </c>
       <c r="L142" s="4" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="M142" s="4">
         <v>0</v>
@@ -8111,40 +8135,40 @@
     </row>
     <row r="143">
       <c r="A143" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>276</v>
+        <v>129</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>101</v>
+        <v>282</v>
       </c>
       <c r="J143" s="4">
         <v>90</v>
       </c>
       <c r="K143" s="4" t="s">
-        <v>276</v>
+        <v>129</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>101</v>
+        <v>282</v>
       </c>
       <c r="M143" s="4">
         <v>0</v>
@@ -8159,40 +8183,40 @@
     </row>
     <row r="144">
       <c r="A144" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>71</v>
+        <v>283</v>
       </c>
       <c r="I144" s="4" t="s">
-        <v>73</v>
+        <v>284</v>
       </c>
       <c r="J144" s="4">
         <v>90</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>71</v>
+        <v>283</v>
       </c>
       <c r="L144" s="4" t="s">
-        <v>73</v>
+        <v>284</v>
       </c>
       <c r="M144" s="4">
         <v>0</v>
@@ -8202,45 +8226,45 @@
         <v>26</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>27</v>
+        <v>285</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B145" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="C145" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E145" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C145" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="F145" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="I145" s="4" t="s">
-        <v>116</v>
+        <v>286</v>
       </c>
       <c r="J145" s="4">
         <v>90</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="L145" s="4" t="s">
-        <v>116</v>
+        <v>286</v>
       </c>
       <c r="M145" s="4">
         <v>0</v>
@@ -8255,40 +8279,40 @@
     </row>
     <row r="146">
       <c r="A146" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B146" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="C146" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E146" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C146" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="F146" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="I146" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J146" s="4">
         <v>90</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M146" s="4">
         <v>0</v>
@@ -8303,40 +8327,40 @@
     </row>
     <row r="147">
       <c r="A147" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="I147" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J147" s="4">
         <v>480</v>
       </c>
       <c r="K147" s="4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M147" s="4">
         <v>0</v>
@@ -8351,40 +8375,40 @@
     </row>
     <row r="148">
       <c r="A148" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B148" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="C148" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E148" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C148" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E148" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="F148" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>145</v>
+        <v>287</v>
       </c>
       <c r="I148" s="4" t="s">
-        <v>84</v>
+        <v>288</v>
       </c>
       <c r="J148" s="4">
         <v>90</v>
       </c>
       <c r="K148" s="4" t="s">
-        <v>145</v>
+        <v>287</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>84</v>
+        <v>288</v>
       </c>
       <c r="M148" s="4">
         <v>0</v>
@@ -8399,40 +8423,40 @@
     </row>
     <row r="149">
       <c r="A149" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="C149" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E149" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C149" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>283</v>
-      </c>
       <c r="F149" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="I149" s="4" t="s">
-        <v>33</v>
+        <v>289</v>
       </c>
       <c r="J149" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K149" s="4" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="L149" s="4" t="s">
-        <v>33</v>
+        <v>289</v>
       </c>
       <c r="M149" s="4">
         <v>0</v>
@@ -8447,40 +8471,40 @@
     </row>
     <row r="150">
       <c r="A150" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B150" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="C150" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E150" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C150" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D150" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="F150" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="I150" s="4" t="s">
-        <v>147</v>
+        <v>290</v>
       </c>
       <c r="J150" s="4">
         <v>90</v>
       </c>
       <c r="K150" s="4" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>147</v>
+        <v>290</v>
       </c>
       <c r="M150" s="4">
         <v>0</v>
@@ -8495,40 +8519,40 @@
     </row>
     <row r="151">
       <c r="A151" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="I151" s="4" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="J151" s="4">
         <v>90</v>
       </c>
       <c r="K151" s="4" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="L151" s="4" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="M151" s="4">
         <v>0</v>
@@ -8543,40 +8567,40 @@
     </row>
     <row r="152">
       <c r="A152" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B152" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="C152" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E152" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C152" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>283</v>
-      </c>
       <c r="F152" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="I152" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J152" s="4">
         <v>480</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="M152" s="4">
         <v>0</v>
@@ -8591,40 +8615,40 @@
     </row>
     <row r="153">
       <c r="A153" s="3" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>279</v>
+        <v>242</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>287</v>
+        <v>39</v>
       </c>
       <c r="J153" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K153" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>287</v>
+        <v>39</v>
       </c>
       <c r="M153" s="4">
         <v>0</v>
@@ -8639,40 +8663,40 @@
     </row>
     <row r="154">
       <c r="A154" s="3" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="I154" s="4" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="J154" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K154" s="4" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="L154" s="4" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="M154" s="4">
         <v>0</v>
@@ -8687,40 +8711,40 @@
     </row>
     <row r="155">
       <c r="A155" s="3" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I155" s="4" t="s">
-        <v>288</v>
+        <v>129</v>
       </c>
       <c r="J155" s="4">
         <v>90</v>
       </c>
       <c r="K155" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L155" s="4" t="s">
-        <v>288</v>
+        <v>129</v>
       </c>
       <c r="M155" s="4">
         <v>0</v>
@@ -8735,40 +8759,40 @@
     </row>
     <row r="156">
       <c r="A156" s="3" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="I156" s="4" t="s">
-        <v>289</v>
+        <v>140</v>
       </c>
       <c r="J156" s="4">
         <v>90</v>
       </c>
       <c r="K156" s="4" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="L156" s="4" t="s">
-        <v>289</v>
+        <v>140</v>
       </c>
       <c r="M156" s="4">
         <v>0</v>
@@ -8783,40 +8807,40 @@
     </row>
     <row r="157">
       <c r="A157" s="3" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="I157" s="4" t="s">
-        <v>291</v>
+        <v>118</v>
       </c>
       <c r="J157" s="4">
         <v>90</v>
       </c>
       <c r="K157" s="4" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>291</v>
+        <v>118</v>
       </c>
       <c r="M157" s="4">
         <v>0</v>
@@ -8831,40 +8855,40 @@
     </row>
     <row r="158">
       <c r="A158" s="3" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>293</v>
+        <v>34</v>
       </c>
       <c r="I158" s="4" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="J158" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K158" s="4" t="s">
-        <v>293</v>
+        <v>34</v>
       </c>
       <c r="L158" s="4" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="M158" s="4">
         <v>0</v>
@@ -8879,40 +8903,40 @@
     </row>
     <row r="159">
       <c r="A159" s="3" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="I159" s="4" t="s">
-        <v>294</v>
+        <v>112</v>
       </c>
       <c r="J159" s="4">
         <v>90</v>
       </c>
       <c r="K159" s="4" t="s">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="L159" s="4" t="s">
-        <v>294</v>
+        <v>112</v>
       </c>
       <c r="M159" s="4">
         <v>0</v>
@@ -8927,40 +8951,40 @@
     </row>
     <row r="160">
       <c r="A160" s="3" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>147</v>
+        <v>42</v>
       </c>
       <c r="I160" s="4" t="s">
-        <v>295</v>
+        <v>145</v>
       </c>
       <c r="J160" s="4">
         <v>90</v>
       </c>
       <c r="K160" s="4" t="s">
-        <v>147</v>
+        <v>42</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>295</v>
+        <v>145</v>
       </c>
       <c r="M160" s="4">
         <v>0</v>
@@ -8975,40 +8999,40 @@
     </row>
     <row r="161">
       <c r="A161" s="3" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I161" s="4" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="J161" s="4">
         <v>480</v>
       </c>
       <c r="K161" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L161" s="4" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="M161" s="4">
         <v>0</v>
@@ -9018,6 +9042,150 @@
         <v>26</v>
       </c>
       <c r="P161" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I162" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="J162" s="4">
+        <v>90</v>
+      </c>
+      <c r="K162" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L162" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="M162" s="4">
+        <v>0</v>
+      </c>
+      <c r="N162" s="3"/>
+      <c r="O162" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P162" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="I163" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J163" s="4">
+        <v>90</v>
+      </c>
+      <c r="K163" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="L163" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M163" s="4">
+        <v>0</v>
+      </c>
+      <c r="N163" s="3"/>
+      <c r="O163" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P163" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I164" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J164" s="4">
+        <v>90</v>
+      </c>
+      <c r="K164" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="L164" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="M164" s="4">
+        <v>0</v>
+      </c>
+      <c r="N164" s="3"/>
+      <c r="O164" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P164" s="4" t="s">
         <v>27</v>
       </c>
     </row>

--- a/data/hrm_sync_actual_1.xlsx
+++ b/data/hrm_sync_actual_1.xlsx
@@ -70,37 +70,130 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>09/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 19:30:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02021645</t>
+  </si>
+  <si>
+    <t>Trịnh Xuân Tỉnh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>12/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02022158</t>
+  </si>
+  <si>
+    <t>Bùi Lê Đức Minh</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 2)</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02325295</t>
+  </si>
+  <si>
+    <t>Lưu Văn Đủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
+  </si>
+  <si>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
     <t>02224288</t>
   </si>
   <si>
     <t>Võ Văn Dương</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
     <t>tăng ca lắp rack bonbin</t>
   </si>
   <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
     <t>21/09/2026 14:00:00</t>
   </si>
   <si>
     <t>21/09/2026 16:00:00</t>
   </si>
   <si>
-    <t>Bằng KH</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
+    <t>Hỗ trợ sản xuất(ca 3)</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/09/2026 06:00:00</t>
   </si>
   <si>
     <t>02645278</t>
@@ -118,13 +211,394 @@
     <t>03/09/2026 22:00:00</t>
   </si>
   <si>
-    <t xml:space="preserve">tăng ca sản xuất </t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 22:00:00</t>
+    <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
+  </si>
+  <si>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>Kiểm kê kho tháng 9.</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất(ca2)</t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
+  </si>
+  <si>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>16/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
+  </si>
+  <si>
+    <t>09/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>Lớn hơn KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>07/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>07/09/2026 18:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>11/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>11/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>10/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>10/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02516134</t>
+  </si>
+  <si>
+    <t>Ngô Xuân Nghĩa</t>
+  </si>
+  <si>
+    <t>Thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bobin</t>
+  </si>
+  <si>
+    <t>thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca1</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>lắp rack bobin tại xưởng 3</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
+  </si>
+  <si>
+    <t>02645269</t>
+  </si>
+  <si>
+    <t>Lê Thanh Toàn</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>10/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02325374</t>
+  </si>
+  <si>
+    <t>Trương Văn Tình</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>Tăng ca sản xuất ( Ca 2 )</t>
+  </si>
+  <si>
+    <t>16/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca2</t>
+  </si>
+  <si>
+    <t>16/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca3 </t>
+  </si>
+  <si>
+    <t>11/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>01921560</t>
+  </si>
+  <si>
+    <t>Trần Quang Hiệu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
+  </si>
+  <si>
+    <t>Tăng ca lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>08/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>08/09/2026 19:30:00</t>
+  </si>
+  <si>
+    <t>02619486</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
   </si>
   <si>
     <t>02021159</t>
@@ -133,55 +607,43 @@
     <t>Trần Vương</t>
   </si>
   <si>
+    <t>tăng ca sản xuất : ca 1</t>
+  </si>
+  <si>
     <t>tăng ca sản xuất ca 2</t>
   </si>
   <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
-  </si>
-  <si>
-    <t>22/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất : ca 1</t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>Tăng ca sản xuất</t>
   </si>
   <si>
     <t>tăng ca hổ trợ nghiền ca 2</t>
   </si>
   <si>
-    <t>02516134</t>
-  </si>
-  <si>
-    <t>Ngô Xuân Nghĩa</t>
-  </si>
-  <si>
-    <t>Thực hiện dự án cải tiến</t>
-  </si>
-  <si>
-    <t>19/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>02020488</t>
-  </si>
-  <si>
-    <t>Lê Thanh Trúc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hỗ trợ sản xuất </t>
   </si>
   <si>
     <t>02220255</t>
@@ -193,55 +655,10 @@
     <t>tăng ca lắp rack xưởng 3</t>
   </si>
   <si>
-    <t>14/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>Lớn hơn KH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>02222785</t>
-  </si>
-  <si>
-    <t>Nguyễn Anh Duy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
-  </si>
-  <si>
-    <t>02022158</t>
-  </si>
-  <si>
-    <t>Bùi Lê Đức Minh</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất(ca 3)</t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>02229894</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tài</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca1</t>
-  </si>
-  <si>
-    <t>12/09/2026 06:00:00</t>
+    <t xml:space="preserve">lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca 2</t>
   </si>
   <si>
     <t>02022149</t>
@@ -250,412 +667,25 @@
     <t>Nguyễn Xuân Mạnh</t>
   </si>
   <si>
-    <t>thực hiện dự án cải tiến</t>
-  </si>
-  <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t>10/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>10/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất(ca 2)</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>20/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
-  </si>
-  <si>
-    <t>02411884</t>
-  </si>
-  <si>
-    <t>Phan Đình Lâm</t>
-  </si>
-  <si>
-    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>02227708</t>
-  </si>
-  <si>
-    <t>Phạm Việt Khải</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
-  </si>
-  <si>
-    <t>09/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 19:30:00</t>
-  </si>
-  <si>
-    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
-  </si>
-  <si>
-    <t>09/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02241656</t>
-  </si>
-  <si>
-    <t>Lương Trọng Ân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca3 </t>
-  </si>
-  <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>02020752</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất(ca2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lắp rack xưởng 3 </t>
-  </si>
-  <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>24/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>Chờ cấp trên gian tiếp</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca2</t>
-  </si>
-  <si>
-    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>02224367</t>
-  </si>
-  <si>
-    <t>Ngô Minh Hiếu</t>
-  </si>
-  <si>
-    <t>02325295</t>
-  </si>
-  <si>
-    <t>Lưu Văn Đủ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
-  </si>
-  <si>
-    <t>hổ trợ nghiền</t>
-  </si>
-  <si>
-    <t>16/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bobin</t>
-  </si>
-  <si>
-    <t>01921551</t>
-  </si>
-  <si>
-    <t>Trương Quang Nghĩa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hỗ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
-    <t>Kiểm kê kho tháng 9.</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t>11/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>02021645</t>
-  </si>
-  <si>
-    <t>Trịnh Xuân Tỉnh</t>
-  </si>
-  <si>
-    <t>02645269</t>
-  </si>
-  <si>
-    <t>Lê Thanh Toàn</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>10/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>02619486</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Huy</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>07/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>07/09/2026 18:30:00</t>
-  </si>
-  <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>17/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>02020965</t>
-  </si>
-  <si>
-    <t>Hà Xuân Tiến</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
-  </si>
-  <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
-  </si>
-  <si>
-    <t>lắp rack bobin tại xưởng 3</t>
-  </si>
-  <si>
-    <t>02325374</t>
-  </si>
-  <si>
-    <t>Trương Văn Tình</t>
-  </si>
-  <si>
-    <t>Tăng ca sản xuất ( Ca 2 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
-  </si>
-  <si>
-    <t>16/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
-  </si>
-  <si>
-    <t>18/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>Tăng ca lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>02519007</t>
-  </si>
-  <si>
-    <t>Ninh Quang Trường</t>
-  </si>
-  <si>
-    <t>15/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>08/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>08/09/2026 19:30:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02020390</t>
-  </si>
-  <si>
-    <t>Võ Thiên Tuế</t>
-  </si>
-  <si>
-    <t>Tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>01921560</t>
-  </si>
-  <si>
-    <t>Trần Quang Hiệu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
+    <t>02325365</t>
+  </si>
+  <si>
+    <t>Trần Minh Nhật</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất (ca 3)</t>
+  </si>
+  <si>
+    <t>02325310</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Hậu</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất (ca3)</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ( ca 1)</t>
   </si>
   <si>
     <t>02021131</t>
@@ -682,54 +712,21 @@
     <t>Trần Xuân Bắc</t>
   </si>
   <si>
+    <t xml:space="preserve">Tăng ca thứ 7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
+  </si>
+  <si>
     <t>Tăng ca hỗ trợ nghiền CA 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Tăng ca thứ 7 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
-  </si>
-  <si>
     <t>17/09/2026 20:30:00</t>
   </si>
   <si>
     <t>17/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>02021742</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Dũng</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca 2</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca 1</t>
-  </si>
-  <si>
-    <t>02325365</t>
-  </si>
-  <si>
-    <t>Trần Minh Nhật</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất (ca 3)</t>
-  </si>
-  <si>
-    <t>02325310</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Hậu</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất (ca3)</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ( ca 1)</t>
-  </si>
-  <si>
     <t>01920862</t>
   </si>
   <si>
@@ -754,12 +751,12 @@
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
+    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
+  </si>
+  <si>
     <t>chuẩn bị kiểm kê</t>
   </si>
   <si>
-    <t xml:space="preserve">vận chuyển nguyên vật liệu nghiền </t>
-  </si>
-  <si>
     <t>23/09/2026 16:30:00</t>
   </si>
   <si>
@@ -778,13 +775,46 @@
     <t>24/09/2026 18:00:00</t>
   </si>
   <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
     <t>02222350</t>
   </si>
   <si>
     <t>Hoàng Văn Nguyên</t>
   </si>
   <si>
-    <t>Tăng cường sản xuất</t>
+    <t>02226596</t>
+  </si>
+  <si>
+    <t>Đoàn Văn Dương</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>02228947</t>
+  </si>
+  <si>
+    <t>Phạm Lê Minh Tân</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>Tăng Cường Sản Xuất</t>
   </si>
   <si>
     <t>02223605</t>
@@ -793,21 +823,6 @@
     <t>Võ Minh Bắc</t>
   </si>
   <si>
-    <t>02223526</t>
-  </si>
-  <si>
-    <t>Nguyễn Thiên Phú</t>
-  </si>
-  <si>
-    <t>02226596</t>
-  </si>
-  <si>
-    <t>Đoàn Văn Dương</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:00:00</t>
-  </si>
-  <si>
     <t>02224358</t>
   </si>
   <si>
@@ -817,25 +832,13 @@
     <t>ca1 tăng ca sản xuất</t>
   </si>
   <si>
-    <t>02228947</t>
-  </si>
-  <si>
-    <t>Phạm Lê Minh Tân</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất</t>
-  </si>
-  <si>
     <t xml:space="preserve">ca2 Tăng ca hỗ trợ Nghiền </t>
   </si>
   <si>
-    <t>02243654</t>
-  </si>
-  <si>
-    <t>Lưu Văn Giang</t>
-  </si>
-  <si>
-    <t>Tăng Cường Sản Xuất</t>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
   </si>
   <si>
     <t>02644057</t>
@@ -847,13 +850,40 @@
     <t>tăng ca đáp ứng tiến độ sản xuất</t>
   </si>
   <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>tang ca cat ong nhua</t>
+  </si>
+  <si>
     <t>22/09/2026 12:30:00</t>
   </si>
   <si>
+    <t>18/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tang ca cat ong nhua </t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>24/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
+    <t>21/09/2026 12:30:00</t>
+  </si>
+  <si>
     <t>23/09/2026 12:30:00</t>
   </si>
   <si>
-    <t>21/09/2026 12:30:00</t>
+    <t>21/09/2026 15:30:00</t>
   </si>
   <si>
     <t>02644075</t>
@@ -868,18 +898,21 @@
     <t>17/09/2026 15:30:00</t>
   </si>
   <si>
+    <t>16/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca cǎt ông nhua</t>
+  </si>
+  <si>
+    <t>14/09/2026 12:30:00</t>
+  </si>
+  <si>
     <t>23/09/2026 20:30:00</t>
   </si>
   <si>
     <t>23/09/2026 22:00:00</t>
   </si>
   <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
-    <t>16/09/2026 15:30:00</t>
-  </si>
-  <si>
     <t>22/09/2026 20:30:00</t>
   </si>
   <si>
@@ -896,39 +929,6 @@
   </si>
   <si>
     <t>21/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02622116</t>
-  </si>
-  <si>
-    <t>Trịnh Nhựt Khánh</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>tang ca cat ong nhua</t>
-  </si>
-  <si>
-    <t>18/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tang ca cat ong nhua </t>
-  </si>
-  <si>
-    <t>21/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca cǎt ông nhua</t>
-  </si>
-  <si>
-    <t>14/09/2026 12:30:00</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +1442,7 @@
         <v>25</v>
       </c>
       <c r="J3" s="8">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>24</v>
@@ -1463,40 +1463,40 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="J4" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>19</v>
@@ -1523,28 +1523,28 @@
         <v>20</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="J5" s="8">
         <v>480</v>
       </c>
       <c r="K5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="M5" s="8">
         <v>0</v>
@@ -1559,40 +1559,40 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="J6" s="8">
         <v>480</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M6" s="8">
         <v>0</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>19</v>
@@ -1619,7 +1619,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -1628,19 +1628,19 @@
         <v>23</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J7" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M7" s="8">
         <v>0</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>19</v>
@@ -1667,7 +1667,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>22</v>
@@ -1676,19 +1676,19 @@
         <v>23</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J8" s="8">
         <v>480</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M8" s="8">
         <v>0</v>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>19</v>
@@ -1724,19 +1724,19 @@
         <v>23</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="J9" s="8">
         <v>480</v>
       </c>
       <c r="K9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="M9" s="8">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J10" s="8">
         <v>480</v>
@@ -1784,7 +1784,7 @@
         <v>50</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M10" s="8">
         <v>0</v>
@@ -1799,40 +1799,40 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>39</v>
-      </c>
       <c r="I11" s="8" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J11" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="M11" s="8">
         <v>0</v>
@@ -1847,47 +1847,47 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="8" t="s">
+      <c r="I12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="J12" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="L12" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="M12" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N12" s="7"/>
       <c r="O12" s="8" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="P12" s="8" t="s">
         <v>27</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>19</v>
@@ -1907,28 +1907,28 @@
         <v>20</v>
       </c>
       <c r="E13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="I13" s="8" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="J13" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="M13" s="8">
         <v>0</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>19</v>
@@ -1955,7 +1955,7 @@
         <v>20</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>22</v>
@@ -1967,7 +1967,7 @@
         <v>39</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J14" s="8">
         <v>480</v>
@@ -1976,7 +1976,7 @@
         <v>39</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="M14" s="8">
         <v>0</v>
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>19</v>
@@ -2003,7 +2003,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>22</v>
@@ -2012,19 +2012,19 @@
         <v>23</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J15" s="8">
         <v>480</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="M15" s="8">
         <v>0</v>
@@ -2039,40 +2039,40 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="F16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="I16" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="J16" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M16" s="8">
         <v>0</v>
@@ -2087,11 +2087,11 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>72</v>
-      </c>
       <c r="C17" s="7" t="s">
         <v>19</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>22</v>
@@ -2108,19 +2108,19 @@
         <v>23</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J17" s="8">
         <v>480</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M17" s="8">
         <v>0</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>19</v>
@@ -2147,7 +2147,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>22</v>
@@ -2156,19 +2156,19 @@
         <v>23</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J18" s="8">
         <v>480</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M18" s="8">
         <v>0</v>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>19</v>
@@ -2204,19 +2204,19 @@
         <v>23</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="J19" s="8">
         <v>480</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="M19" s="8">
         <v>0</v>
@@ -2231,20 +2231,20 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="F20" s="7" t="s">
         <v>22</v>
       </c>
@@ -2252,19 +2252,19 @@
         <v>23</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="J20" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="M20" s="8">
         <v>0</v>
@@ -2279,10 +2279,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>19</v>
@@ -2291,7 +2291,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>22</v>
@@ -2300,19 +2300,19 @@
         <v>23</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J21" s="8">
         <v>480</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M21" s="8">
         <v>0</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>19</v>
@@ -2339,7 +2339,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>22</v>
@@ -2348,19 +2348,19 @@
         <v>23</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="J22" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="M22" s="8">
         <v>0</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>19</v>
@@ -2387,25 +2387,25 @@
         <v>20</v>
       </c>
       <c r="E23" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>88</v>
       </c>
       <c r="J23" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>88</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>19</v>
@@ -2444,19 +2444,19 @@
         <v>23</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J24" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M24" s="8">
         <v>0</v>
@@ -2471,40 +2471,40 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J25" s="8">
         <v>90</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="7" t="s">
+      <c r="K25" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="J25" s="8">
-        <v>480</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="L25" s="8" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="M25" s="8">
         <v>0</v>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>19</v>
@@ -2531,7 +2531,7 @@
         <v>20</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>22</v>
@@ -2540,19 +2540,19 @@
         <v>23</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J26" s="8">
         <v>480</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M26" s="8">
         <v>0</v>
@@ -2567,10 +2567,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>19</v>
@@ -2579,7 +2579,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>22</v>
@@ -2588,19 +2588,19 @@
         <v>23</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J27" s="8">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M27" s="8">
         <v>0</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>19</v>
@@ -2627,7 +2627,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>22</v>
@@ -2636,19 +2636,19 @@
         <v>23</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="J28" s="8">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="M28" s="8">
         <v>0</v>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>19</v>
@@ -2675,7 +2675,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>22</v>
@@ -2684,26 +2684,26 @@
         <v>23</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="J29" s="8">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="M29" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N29" s="7"/>
       <c r="O29" s="8" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="P29" s="8" t="s">
         <v>27</v>
@@ -2711,10 +2711,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>19</v>
@@ -2723,7 +2723,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>22</v>
@@ -2732,19 +2732,19 @@
         <v>23</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="J30" s="4">
         <v>480</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="M30" s="4">
         <v>0</v>
@@ -2759,20 +2759,20 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="F31" s="3" t="s">
         <v>22</v>
       </c>
@@ -2780,19 +2780,19 @@
         <v>23</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J31" s="4">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="M31" s="4">
         <v>0</v>
@@ -2807,10 +2807,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>19</v>
@@ -2819,7 +2819,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>22</v>
@@ -2828,19 +2828,19 @@
         <v>23</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="J32" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="M32" s="4">
         <v>0</v>
@@ -2855,19 +2855,19 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>22</v>
@@ -2876,19 +2876,19 @@
         <v>23</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="J33" s="4">
         <v>480</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="M33" s="4">
         <v>0</v>
@@ -2903,19 +2903,19 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>22</v>
@@ -2924,19 +2924,19 @@
         <v>23</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="J34" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="M34" s="4">
         <v>0</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>19</v>
@@ -2963,7 +2963,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>22</v>
@@ -2972,19 +2972,19 @@
         <v>23</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J35" s="4">
         <v>480</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M35" s="4">
         <v>0</v>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
@@ -3011,28 +3011,28 @@
         <v>20</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>112</v>
-      </c>
       <c r="I36" s="4" t="s">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="J36" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="M36" s="4">
         <v>0</v>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>19</v>
@@ -3059,7 +3059,7 @@
         <v>20</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>22</v>
@@ -3068,26 +3068,26 @@
         <v>23</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="J37" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="M37" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="4" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="P37" s="4" t="s">
         <v>27</v>
@@ -3095,19 +3095,19 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>22</v>
@@ -3116,19 +3116,19 @@
         <v>23</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="J38" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="M38" s="4">
         <v>0</v>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
@@ -3155,7 +3155,7 @@
         <v>20</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>22</v>
@@ -3164,19 +3164,19 @@
         <v>23</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J39" s="4">
         <v>120</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M39" s="4">
         <v>0</v>
@@ -3191,19 +3191,19 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>22</v>
@@ -3234,15 +3234,15 @@
         <v>26</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
@@ -3251,28 +3251,28 @@
         <v>20</v>
       </c>
       <c r="E41" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="I41" s="4" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="J41" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="M41" s="4">
         <v>0</v>
@@ -3287,40 +3287,40 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="I42" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J42" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M42" s="4">
         <v>0</v>
@@ -3335,10 +3335,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
@@ -3347,7 +3347,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>22</v>
@@ -3356,19 +3356,19 @@
         <v>23</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J43" s="4">
         <v>90</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M43" s="4">
         <v>0</v>
@@ -3383,10 +3383,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
@@ -3395,7 +3395,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>22</v>
@@ -3404,19 +3404,19 @@
         <v>23</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J44" s="4">
         <v>480</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M44" s="4">
         <v>0</v>
@@ -3452,19 +3452,19 @@
         <v>23</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J45" s="4">
         <v>480</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M45" s="4">
         <v>0</v>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>19</v>
@@ -3500,19 +3500,19 @@
         <v>23</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="J46" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="M46" s="4">
         <v>0</v>
@@ -3527,10 +3527,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>19</v>
@@ -3539,7 +3539,7 @@
         <v>20</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>22</v>
@@ -3548,19 +3548,19 @@
         <v>23</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="J47" s="4">
         <v>480</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="M47" s="4">
         <v>0</v>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>19</v>
@@ -3587,7 +3587,7 @@
         <v>20</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>22</v>
@@ -3596,19 +3596,19 @@
         <v>23</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="J48" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="M48" s="4">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>19</v>
@@ -3635,28 +3635,28 @@
         <v>20</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J49" s="4">
         <v>120</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="I49" s="4" t="s">
+      <c r="K49" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="J49" s="4">
-        <v>90</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="L49" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M49" s="4">
         <v>0</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>19</v>
@@ -3683,7 +3683,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>22</v>
@@ -3692,19 +3692,19 @@
         <v>23</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J50" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M50" s="4">
         <v>0</v>
@@ -3719,40 +3719,40 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="3" t="s">
+      <c r="I51" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F51" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="J51" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="M51" s="4">
         <v>0</v>
@@ -3767,19 +3767,19 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>22</v>
@@ -3788,19 +3788,19 @@
         <v>23</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="J52" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="M52" s="4">
         <v>0</v>
@@ -3815,10 +3815,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>19</v>
@@ -3827,7 +3827,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>22</v>
@@ -3836,19 +3836,19 @@
         <v>23</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="J53" s="4">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="M53" s="4">
         <v>0</v>
@@ -3863,20 +3863,20 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="F54" s="3" t="s">
         <v>22</v>
       </c>
@@ -3884,19 +3884,19 @@
         <v>23</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J54" s="4">
         <v>480</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M54" s="4">
         <v>0</v>
@@ -3911,10 +3911,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>19</v>
@@ -3923,7 +3923,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>22</v>
@@ -3932,19 +3932,19 @@
         <v>23</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J55" s="4">
         <v>90</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M55" s="4">
         <v>0</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>19</v>
@@ -3971,7 +3971,7 @@
         <v>20</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>22</v>
@@ -3980,19 +3980,19 @@
         <v>23</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="J56" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="M56" s="4">
         <v>0</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>19</v>
@@ -4019,7 +4019,7 @@
         <v>20</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>22</v>
@@ -4028,19 +4028,19 @@
         <v>23</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="J57" s="4">
         <v>480</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="M57" s="4">
         <v>0</v>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>19</v>
@@ -4067,7 +4067,7 @@
         <v>20</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>22</v>
@@ -4076,19 +4076,19 @@
         <v>23</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>156</v>
+        <v>33</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>157</v>
+        <v>34</v>
       </c>
       <c r="J58" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>156</v>
+        <v>33</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>157</v>
+        <v>34</v>
       </c>
       <c r="M58" s="4">
         <v>0</v>
@@ -4103,10 +4103,10 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>19</v>
@@ -4115,7 +4115,7 @@
         <v>20</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>33</v>
+        <v>153</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>22</v>
@@ -4124,19 +4124,19 @@
         <v>23</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="J59" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="M59" s="4">
         <v>0</v>
@@ -4151,10 +4151,10 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>19</v>
@@ -4163,7 +4163,7 @@
         <v>20</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>22</v>
@@ -4172,19 +4172,19 @@
         <v>23</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>163</v>
+        <v>57</v>
       </c>
       <c r="J60" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>163</v>
+        <v>57</v>
       </c>
       <c r="M60" s="4">
         <v>0</v>
@@ -4199,10 +4199,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>19</v>
@@ -4211,28 +4211,28 @@
         <v>20</v>
       </c>
       <c r="E61" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="I61" s="4" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="J61" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="M61" s="4">
         <v>0</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>19</v>
@@ -4259,7 +4259,7 @@
         <v>20</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>22</v>
@@ -4268,19 +4268,19 @@
         <v>23</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="J62" s="4">
         <v>480</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="M62" s="4">
         <v>0</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>19</v>
@@ -4307,7 +4307,7 @@
         <v>20</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>22</v>
@@ -4316,19 +4316,19 @@
         <v>23</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>39</v>
+        <v>167</v>
       </c>
       <c r="J63" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>39</v>
+        <v>167</v>
       </c>
       <c r="M63" s="4">
         <v>0</v>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>19</v>
@@ -4364,19 +4364,19 @@
         <v>23</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="J64" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="M64" s="4">
         <v>0</v>
@@ -4391,10 +4391,10 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>19</v>
@@ -4403,7 +4403,7 @@
         <v>20</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>22</v>
@@ -4412,19 +4412,19 @@
         <v>23</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="J65" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="M65" s="4">
         <v>0</v>
@@ -4439,40 +4439,40 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I66" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>175</v>
       </c>
       <c r="J66" s="4">
         <v>120</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M66" s="4">
         <v>0</v>
@@ -4487,10 +4487,10 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>19</v>
@@ -4499,7 +4499,7 @@
         <v>20</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>22</v>
@@ -4508,19 +4508,19 @@
         <v>23</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>177</v>
+        <v>58</v>
       </c>
       <c r="J67" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>177</v>
+        <v>58</v>
       </c>
       <c r="M67" s="4">
         <v>0</v>
@@ -4535,10 +4535,10 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>19</v>
@@ -4547,28 +4547,28 @@
         <v>20</v>
       </c>
       <c r="E68" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I68" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I68" s="4" t="s">
+      <c r="J68" s="4">
+        <v>90</v>
+      </c>
+      <c r="K68" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="J68" s="4">
-        <v>120</v>
-      </c>
-      <c r="K68" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="L68" s="4" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="M68" s="4">
         <v>0</v>
@@ -4583,10 +4583,10 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>19</v>
@@ -4595,7 +4595,7 @@
         <v>20</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>22</v>
@@ -4604,19 +4604,19 @@
         <v>23</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="J69" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="M69" s="4">
         <v>0</v>
@@ -4631,10 +4631,10 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>19</v>
@@ -4643,7 +4643,7 @@
         <v>20</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>22</v>
@@ -4652,19 +4652,19 @@
         <v>23</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>45</v>
+        <v>175</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>34</v>
+        <v>176</v>
       </c>
       <c r="J70" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>45</v>
+        <v>175</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>34</v>
+        <v>176</v>
       </c>
       <c r="M70" s="4">
         <v>0</v>
@@ -4679,19 +4679,19 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>22</v>
@@ -4700,19 +4700,19 @@
         <v>23</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="J71" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="M71" s="4">
         <v>0</v>
@@ -4727,19 +4727,19 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>22</v>
@@ -4748,19 +4748,19 @@
         <v>23</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="J72" s="4">
         <v>480</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="M72" s="4">
         <v>0</v>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>19</v>
@@ -4787,7 +4787,7 @@
         <v>20</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>188</v>
+        <v>49</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>22</v>
@@ -4796,19 +4796,19 @@
         <v>23</v>
       </c>
       <c r="H73" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I73" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="J73" s="4">
         <v>480</v>
       </c>
       <c r="K73" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L73" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="L73" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="M73" s="4">
         <v>0</v>
@@ -4823,10 +4823,10 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>19</v>
@@ -4835,7 +4835,7 @@
         <v>20</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>22</v>
@@ -4844,19 +4844,19 @@
         <v>23</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="J74" s="4">
         <v>120</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="M74" s="4">
         <v>0</v>
@@ -4871,10 +4871,10 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>19</v>
@@ -4883,7 +4883,7 @@
         <v>20</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>22</v>
@@ -4892,26 +4892,26 @@
         <v>23</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>191</v>
+        <v>112</v>
       </c>
       <c r="J75" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>191</v>
+        <v>113</v>
       </c>
       <c r="M75" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N75" s="3"/>
       <c r="O75" s="4" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="P75" s="4" t="s">
         <v>27</v>
@@ -4919,47 +4919,47 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="J76" s="4">
+        <v>120</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="L76" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J76" s="4">
-        <v>480</v>
-      </c>
-      <c r="K76" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="M76" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N76" s="3"/>
       <c r="O76" s="4" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="P76" s="4" t="s">
         <v>27</v>
@@ -4967,10 +4967,10 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>19</v>
@@ -4979,7 +4979,7 @@
         <v>20</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>22</v>
@@ -4988,19 +4988,19 @@
         <v>23</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J77" s="4">
         <v>120</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="M77" s="4">
         <v>0</v>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>19</v>
@@ -5027,7 +5027,7 @@
         <v>20</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>22</v>
@@ -5036,19 +5036,19 @@
         <v>23</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>193</v>
+        <v>35</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="J78" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>193</v>
+        <v>35</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="M78" s="4">
         <v>0</v>
@@ -5063,10 +5063,10 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>19</v>
@@ -5084,19 +5084,19 @@
         <v>23</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="J79" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="M79" s="4">
         <v>0</v>
@@ -5111,10 +5111,10 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>19</v>
@@ -5123,7 +5123,7 @@
         <v>20</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>22</v>
@@ -5132,19 +5132,19 @@
         <v>23</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J80" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="M80" s="4">
         <v>0</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>19</v>
@@ -5171,7 +5171,7 @@
         <v>20</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>22</v>
@@ -5180,26 +5180,26 @@
         <v>23</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>59</v>
+        <v>191</v>
       </c>
       <c r="J81" s="4">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>60</v>
+        <v>191</v>
       </c>
       <c r="M81" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N81" s="3"/>
       <c r="O81" s="4" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="P81" s="4" t="s">
         <v>27</v>
@@ -5207,10 +5207,10 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>19</v>
@@ -5219,7 +5219,7 @@
         <v>20</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>22</v>
@@ -5228,19 +5228,19 @@
         <v>23</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="J82" s="4">
         <v>90</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="M82" s="4">
         <v>0</v>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>19</v>
@@ -5267,7 +5267,7 @@
         <v>20</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>22</v>
@@ -5276,19 +5276,19 @@
         <v>23</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="J83" s="4">
         <v>480</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="M83" s="4">
         <v>0</v>
@@ -5303,20 +5303,20 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="F84" s="3" t="s">
         <v>22</v>
       </c>
@@ -5324,19 +5324,19 @@
         <v>23</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="J84" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="M84" s="4">
         <v>0</v>
@@ -5351,20 +5351,20 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="F85" s="3" t="s">
         <v>22</v>
       </c>
@@ -5372,19 +5372,19 @@
         <v>23</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="J85" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="M85" s="4">
         <v>0</v>
@@ -5399,10 +5399,10 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>19</v>
@@ -5411,7 +5411,7 @@
         <v>20</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>22</v>
@@ -5420,19 +5420,19 @@
         <v>23</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="J86" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="M86" s="4">
         <v>0</v>
@@ -5447,10 +5447,10 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>19</v>
@@ -5459,7 +5459,7 @@
         <v>20</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>22</v>
@@ -5468,19 +5468,19 @@
         <v>23</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>200</v>
+        <v>39</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>201</v>
+        <v>57</v>
       </c>
       <c r="J87" s="4">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>200</v>
+        <v>39</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>201</v>
+        <v>57</v>
       </c>
       <c r="M87" s="4">
         <v>0</v>
@@ -5495,10 +5495,10 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>19</v>
@@ -5507,7 +5507,7 @@
         <v>20</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>22</v>
@@ -5516,19 +5516,19 @@
         <v>23</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>156</v>
+        <v>43</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>202</v>
+        <v>33</v>
       </c>
       <c r="J88" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>156</v>
+        <v>43</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>202</v>
+        <v>33</v>
       </c>
       <c r="M88" s="4">
         <v>0</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>19</v>
@@ -5555,7 +5555,7 @@
         <v>20</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>22</v>
@@ -5564,19 +5564,19 @@
         <v>23</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>177</v>
+        <v>58</v>
       </c>
       <c r="J89" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>177</v>
+        <v>58</v>
       </c>
       <c r="M89" s="4">
         <v>0</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>19</v>
@@ -5603,7 +5603,7 @@
         <v>20</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>22</v>
@@ -5612,19 +5612,19 @@
         <v>23</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>203</v>
+        <v>39</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>204</v>
+        <v>57</v>
       </c>
       <c r="J90" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>203</v>
+        <v>39</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>204</v>
+        <v>57</v>
       </c>
       <c r="M90" s="4">
         <v>0</v>
@@ -5639,10 +5639,10 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>19</v>
@@ -5651,7 +5651,7 @@
         <v>20</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>22</v>
@@ -5660,19 +5660,19 @@
         <v>23</v>
       </c>
       <c r="H91" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I91" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="J91" s="4">
         <v>480</v>
       </c>
       <c r="K91" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L91" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="L91" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="M91" s="4">
         <v>0</v>
@@ -5687,10 +5687,10 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>19</v>
@@ -5699,7 +5699,7 @@
         <v>20</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>86</v>
+        <v>211</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>22</v>
@@ -5708,26 +5708,26 @@
         <v>23</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>74</v>
+        <v>184</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>39</v>
+        <v>185</v>
       </c>
       <c r="J92" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>74</v>
+        <v>184</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>39</v>
+        <v>186</v>
       </c>
       <c r="M92" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" s="4" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="P92" s="4" t="s">
         <v>27</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>19</v>
@@ -5747,7 +5747,7 @@
         <v>20</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>22</v>
@@ -5756,19 +5756,19 @@
         <v>23</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="J93" s="4">
         <v>480</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="M93" s="4">
         <v>0</v>
@@ -5783,10 +5783,10 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>19</v>
@@ -5795,7 +5795,7 @@
         <v>20</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>22</v>
@@ -5804,19 +5804,19 @@
         <v>23</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="J94" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="M94" s="4">
         <v>0</v>
@@ -5831,10 +5831,10 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>19</v>
@@ -5852,26 +5852,26 @@
         <v>23</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="J95" s="4">
         <v>120</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>102</v>
+        <v>172</v>
       </c>
       <c r="M95" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N95" s="3"/>
       <c r="O95" s="4" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="P95" s="4" t="s">
         <v>27</v>
@@ -5879,10 +5879,10 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>19</v>
@@ -5891,7 +5891,7 @@
         <v>20</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>22</v>
@@ -5900,19 +5900,19 @@
         <v>23</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="J96" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="M96" s="4">
         <v>0</v>
@@ -5927,10 +5927,10 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>19</v>
@@ -5939,7 +5939,7 @@
         <v>20</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>141</v>
+        <v>211</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>22</v>
@@ -5948,19 +5948,19 @@
         <v>23</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="J97" s="4">
         <v>120</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="M97" s="4">
         <v>0</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>19</v>
@@ -5987,7 +5987,7 @@
         <v>20</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>63</v>
+        <v>213</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>22</v>
@@ -5996,19 +5996,19 @@
         <v>23</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="J98" s="4">
         <v>480</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="M98" s="4">
         <v>0</v>
@@ -6023,10 +6023,10 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>19</v>
@@ -6035,7 +6035,7 @@
         <v>20</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>22</v>
@@ -6044,19 +6044,19 @@
         <v>23</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J99" s="4">
         <v>480</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M99" s="4">
         <v>0</v>
@@ -6071,10 +6071,10 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>19</v>
@@ -6083,7 +6083,7 @@
         <v>20</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>218</v>
+        <v>109</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>22</v>
@@ -6092,19 +6092,19 @@
         <v>23</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J100" s="4">
         <v>480</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="M100" s="4">
         <v>0</v>
@@ -6119,10 +6119,10 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>19</v>
@@ -6131,7 +6131,7 @@
         <v>20</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>22</v>
@@ -6140,19 +6140,19 @@
         <v>23</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>191</v>
+        <v>34</v>
       </c>
       <c r="J101" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>191</v>
+        <v>34</v>
       </c>
       <c r="M101" s="4">
         <v>0</v>
@@ -6179,7 +6179,7 @@
         <v>20</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>22</v>
@@ -6188,19 +6188,19 @@
         <v>23</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J102" s="4">
         <v>480</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M102" s="4">
         <v>0</v>
@@ -6236,19 +6236,19 @@
         <v>23</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="J103" s="4">
         <v>480</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="M103" s="4">
         <v>0</v>
@@ -6263,10 +6263,10 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>19</v>
@@ -6275,7 +6275,7 @@
         <v>20</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>22</v>
@@ -6284,19 +6284,19 @@
         <v>23</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>193</v>
+        <v>43</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="J104" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>193</v>
+        <v>43</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="M104" s="4">
         <v>0</v>
@@ -6311,10 +6311,10 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>19</v>
@@ -6323,7 +6323,7 @@
         <v>20</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>22</v>
@@ -6332,19 +6332,19 @@
         <v>23</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>225</v>
+        <v>29</v>
       </c>
       <c r="J105" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>225</v>
+        <v>29</v>
       </c>
       <c r="M105" s="4">
         <v>0</v>
@@ -6359,10 +6359,10 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>19</v>
@@ -6371,7 +6371,7 @@
         <v>20</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>22</v>
@@ -6380,19 +6380,19 @@
         <v>23</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J106" s="4">
         <v>480</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M106" s="4">
         <v>0</v>
@@ -6407,10 +6407,10 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>19</v>
@@ -6419,7 +6419,7 @@
         <v>20</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>22</v>
@@ -6428,19 +6428,19 @@
         <v>23</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>34</v>
+        <v>162</v>
       </c>
       <c r="J107" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>34</v>
+        <v>162</v>
       </c>
       <c r="M107" s="4">
         <v>0</v>
@@ -6455,11 +6455,11 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="C108" s="3" t="s">
         <v>19</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>20</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>22</v>
@@ -6476,19 +6476,19 @@
         <v>23</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>35</v>
+        <v>164</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="J108" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>35</v>
+        <v>164</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="M108" s="4">
         <v>0</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>19</v>
@@ -6515,7 +6515,7 @@
         <v>20</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>22</v>
@@ -6524,19 +6524,19 @@
         <v>23</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="J109" s="4">
         <v>480</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="M109" s="4">
         <v>0</v>
@@ -6551,40 +6551,40 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B110" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H110" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C110" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="I110" s="4" t="s">
-        <v>39</v>
+        <v>235</v>
       </c>
       <c r="J110" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>74</v>
+        <v>234</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>39</v>
+        <v>235</v>
       </c>
       <c r="M110" s="4">
         <v>0</v>
@@ -6599,20 +6599,20 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="C111" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="F111" s="3" t="s">
         <v>22</v>
       </c>
@@ -6620,19 +6620,19 @@
         <v>23</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J111" s="4">
         <v>480</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M111" s="4">
         <v>0</v>
@@ -6647,20 +6647,20 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="C112" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E112" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C112" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="F112" s="3" t="s">
         <v>22</v>
       </c>
@@ -6668,19 +6668,19 @@
         <v>23</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="J112" s="4">
         <v>480</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="M112" s="4">
         <v>0</v>
@@ -6695,22 +6695,22 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B113" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="C113" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E113" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="F113" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>22</v>
@@ -6719,7 +6719,7 @@
         <v>39</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J113" s="4">
         <v>480</v>
@@ -6728,7 +6728,7 @@
         <v>39</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="M113" s="4">
         <v>0</v>
@@ -6743,40 +6743,40 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="C114" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E114" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C114" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="F114" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J114" s="4">
         <v>480</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M114" s="4">
         <v>0</v>
@@ -6791,40 +6791,40 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="C115" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E115" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C115" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="F115" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="I115" s="4" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="J115" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="M115" s="4">
         <v>0</v>
@@ -6839,40 +6839,40 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B116" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="C116" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="J116" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="M116" s="4">
         <v>0</v>
@@ -6887,40 +6887,40 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B117" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B117" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="C117" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>245</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H117" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="I117" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="I117" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="J117" s="4">
         <v>90</v>
       </c>
       <c r="K117" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="L117" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="L117" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="M117" s="4">
         <v>0</v>
@@ -6935,40 +6935,40 @@
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B118" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="C118" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="J118" s="4">
         <v>480</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="M118" s="4">
         <v>0</v>
@@ -6983,40 +6983,40 @@
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B119" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="C119" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E119" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H119" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="F119" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H119" s="4" t="s">
+      <c r="I119" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="I119" s="4" t="s">
-        <v>252</v>
       </c>
       <c r="J119" s="4">
         <v>90</v>
       </c>
       <c r="K119" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="L119" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="L119" s="4" t="s">
-        <v>252</v>
       </c>
       <c r="M119" s="4">
         <v>0</v>
@@ -7031,40 +7031,40 @@
     </row>
     <row r="120">
       <c r="A120" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B120" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="C120" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>255</v>
+        <v>81</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I120" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J120" s="4">
         <v>480</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M120" s="4">
         <v>0</v>
@@ -7079,40 +7079,40 @@
     </row>
     <row r="121">
       <c r="A121" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="C121" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E121" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C121" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="F121" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J121" s="4">
         <v>480</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M121" s="4">
         <v>0</v>
@@ -7127,40 +7127,40 @@
     </row>
     <row r="122">
       <c r="A122" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B122" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="C122" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I122" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J122" s="4">
         <v>480</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M122" s="4">
         <v>0</v>
@@ -7175,40 +7175,40 @@
     </row>
     <row r="123">
       <c r="A123" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>242</v>
+        <v>135</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="I123" s="4" t="s">
-        <v>70</v>
+        <v>259</v>
       </c>
       <c r="J123" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>70</v>
+        <v>259</v>
       </c>
       <c r="M123" s="4">
         <v>0</v>
@@ -7223,40 +7223,40 @@
     </row>
     <row r="124">
       <c r="A124" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>111</v>
+        <v>254</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="I124" s="4" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="J124" s="4">
         <v>480</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="M124" s="4">
         <v>0</v>
@@ -7271,40 +7271,40 @@
     </row>
     <row r="125">
       <c r="A125" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>262</v>
+        <v>58</v>
       </c>
       <c r="J125" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>262</v>
+        <v>58</v>
       </c>
       <c r="M125" s="4">
         <v>0</v>
@@ -7319,28 +7319,28 @@
     </row>
     <row r="126">
       <c r="A126" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>34</v>
@@ -7349,7 +7349,7 @@
         <v>480</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="L126" s="4" t="s">
         <v>34</v>
@@ -7367,40 +7367,40 @@
     </row>
     <row r="127">
       <c r="A127" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>183</v>
+        <v>80</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="J127" s="4">
         <v>480</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="M127" s="4">
         <v>0</v>
@@ -7415,40 +7415,40 @@
     </row>
     <row r="128">
       <c r="A128" s="3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I128" s="4" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="J128" s="4">
         <v>480</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="M128" s="4">
         <v>0</v>
@@ -7472,31 +7472,31 @@
         <v>19</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>183</v>
+        <v>80</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I129" s="4" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="J129" s="4">
         <v>480</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="M129" s="4">
         <v>0</v>
@@ -7511,40 +7511,40 @@
     </row>
     <row r="130">
       <c r="A130" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>183</v>
+        <v>80</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>63</v>
+        <v>241</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="I130" s="4" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="J130" s="4">
         <v>480</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M130" s="4">
         <v>0</v>
@@ -7559,40 +7559,40 @@
     </row>
     <row r="131">
       <c r="A131" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E131" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="F131" s="3" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I131" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J131" s="4">
         <v>480</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M131" s="4">
         <v>0</v>
@@ -7607,40 +7607,40 @@
     </row>
     <row r="132">
       <c r="A132" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B132" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E132" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C132" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="F132" s="3" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I132" s="4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="J132" s="4">
         <v>480</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="M132" s="4">
         <v>0</v>
@@ -7655,40 +7655,40 @@
     </row>
     <row r="133">
       <c r="A133" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B133" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="C133" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H133" s="4" t="s">
-        <v>224</v>
+        <v>38</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>225</v>
+        <v>39</v>
       </c>
       <c r="J133" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>224</v>
+        <v>38</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>225</v>
+        <v>39</v>
       </c>
       <c r="M133" s="4">
         <v>0</v>
@@ -7703,40 +7703,40 @@
     </row>
     <row r="134">
       <c r="A134" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B134" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B134" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="C134" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>204</v>
+        <v>34</v>
       </c>
       <c r="J134" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>204</v>
+        <v>34</v>
       </c>
       <c r="M134" s="4">
         <v>0</v>
@@ -7751,40 +7751,40 @@
     </row>
     <row r="135">
       <c r="A135" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="J135" s="4">
         <v>90</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="M135" s="4">
         <v>0</v>
@@ -7799,40 +7799,40 @@
     </row>
     <row r="136">
       <c r="A136" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="I136" s="4" t="s">
-        <v>191</v>
+        <v>144</v>
       </c>
       <c r="J136" s="4">
         <v>90</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>191</v>
+        <v>144</v>
       </c>
       <c r="M136" s="4">
         <v>0</v>
@@ -7847,40 +7847,40 @@
     </row>
     <row r="137">
       <c r="A137" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="J137" s="4">
         <v>90</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="M137" s="4">
         <v>0</v>
@@ -7895,40 +7895,40 @@
     </row>
     <row r="138">
       <c r="A138" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>194</v>
+        <v>106</v>
       </c>
       <c r="J138" s="4">
         <v>90</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="L138" s="4" t="s">
-        <v>194</v>
+        <v>106</v>
       </c>
       <c r="M138" s="4">
         <v>0</v>
@@ -7943,40 +7943,40 @@
     </row>
     <row r="139">
       <c r="A139" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="J139" s="4">
         <v>90</v>
       </c>
       <c r="K139" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="L139" s="4" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="M139" s="4">
         <v>0</v>
@@ -7991,40 +7991,40 @@
     </row>
     <row r="140">
       <c r="A140" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>35</v>
+        <v>281</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="J140" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K140" s="4" t="s">
-        <v>35</v>
+        <v>281</v>
       </c>
       <c r="L140" s="4" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="M140" s="4">
         <v>0</v>
@@ -8039,40 +8039,40 @@
     </row>
     <row r="141">
       <c r="A141" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="I141" s="4" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="J141" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K141" s="4" t="s">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="L141" s="4" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="M141" s="4">
         <v>0</v>
@@ -8087,40 +8087,40 @@
     </row>
     <row r="142">
       <c r="A142" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>278</v>
+        <v>130</v>
       </c>
       <c r="I142" s="4" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="J142" s="4">
         <v>90</v>
       </c>
       <c r="K142" s="4" t="s">
-        <v>278</v>
+        <v>130</v>
       </c>
       <c r="L142" s="4" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="M142" s="4">
         <v>0</v>
@@ -8135,40 +8135,40 @@
     </row>
     <row r="143">
       <c r="A143" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>282</v>
+        <v>34</v>
       </c>
       <c r="J143" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K143" s="4" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>282</v>
+        <v>34</v>
       </c>
       <c r="M143" s="4">
         <v>0</v>
@@ -8183,40 +8183,40 @@
     </row>
     <row r="144">
       <c r="A144" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>283</v>
+        <v>43</v>
       </c>
       <c r="I144" s="4" t="s">
-        <v>284</v>
+        <v>33</v>
       </c>
       <c r="J144" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>283</v>
+        <v>43</v>
       </c>
       <c r="L144" s="4" t="s">
-        <v>284</v>
+        <v>33</v>
       </c>
       <c r="M144" s="4">
         <v>0</v>
@@ -8226,45 +8226,45 @@
         <v>26</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>285</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>106</v>
+        <v>284</v>
       </c>
       <c r="I145" s="4" t="s">
-        <v>286</v>
+        <v>105</v>
       </c>
       <c r="J145" s="4">
         <v>90</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>106</v>
+        <v>284</v>
       </c>
       <c r="L145" s="4" t="s">
-        <v>286</v>
+        <v>105</v>
       </c>
       <c r="M145" s="4">
         <v>0</v>
@@ -8274,45 +8274,45 @@
         <v>26</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>27</v>
+        <v>285</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="I146" s="4" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="J146" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="M146" s="4">
         <v>0</v>
@@ -8327,40 +8327,40 @@
     </row>
     <row r="147">
       <c r="A147" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>39</v>
+        <v>286</v>
       </c>
       <c r="I147" s="4" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J147" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K147" s="4" t="s">
-        <v>39</v>
+        <v>286</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="M147" s="4">
         <v>0</v>
@@ -8375,40 +8375,40 @@
     </row>
     <row r="148">
       <c r="A148" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>287</v>
+        <v>166</v>
       </c>
       <c r="I148" s="4" t="s">
-        <v>288</v>
+        <v>167</v>
       </c>
       <c r="J148" s="4">
         <v>90</v>
       </c>
       <c r="K148" s="4" t="s">
-        <v>287</v>
+        <v>166</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>288</v>
+        <v>167</v>
       </c>
       <c r="M148" s="4">
         <v>0</v>
@@ -8423,40 +8423,40 @@
     </row>
     <row r="149">
       <c r="A149" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="I149" s="4" t="s">
-        <v>289</v>
+        <v>165</v>
       </c>
       <c r="J149" s="4">
         <v>90</v>
       </c>
       <c r="K149" s="4" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="L149" s="4" t="s">
-        <v>289</v>
+        <v>165</v>
       </c>
       <c r="M149" s="4">
         <v>0</v>
@@ -8471,40 +8471,40 @@
     </row>
     <row r="150">
       <c r="A150" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>112</v>
+        <v>287</v>
       </c>
       <c r="I150" s="4" t="s">
-        <v>290</v>
+        <v>143</v>
       </c>
       <c r="J150" s="4">
         <v>90</v>
       </c>
       <c r="K150" s="4" t="s">
-        <v>112</v>
+        <v>287</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>290</v>
+        <v>143</v>
       </c>
       <c r="M150" s="4">
         <v>0</v>
@@ -8519,40 +8519,40 @@
     </row>
     <row r="151">
       <c r="A151" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E151" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B151" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D151" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>281</v>
-      </c>
       <c r="F151" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="I151" s="4" t="s">
-        <v>292</v>
+        <v>149</v>
       </c>
       <c r="J151" s="4">
         <v>90</v>
       </c>
       <c r="K151" s="4" t="s">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="L151" s="4" t="s">
-        <v>292</v>
+        <v>149</v>
       </c>
       <c r="M151" s="4">
         <v>0</v>
@@ -8567,40 +8567,40 @@
     </row>
     <row r="152">
       <c r="A152" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="I152" s="4" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="J152" s="4">
         <v>480</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="M152" s="4">
         <v>0</v>
@@ -8615,40 +8615,40 @@
     </row>
     <row r="153">
       <c r="A153" s="3" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>39</v>
+        <v>288</v>
       </c>
       <c r="J153" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K153" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>39</v>
+        <v>288</v>
       </c>
       <c r="M153" s="4">
         <v>0</v>
@@ -8663,40 +8663,40 @@
     </row>
     <row r="154">
       <c r="A154" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>242</v>
+        <v>291</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="I154" s="4" t="s">
-        <v>88</v>
+        <v>292</v>
       </c>
       <c r="J154" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K154" s="4" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="L154" s="4" t="s">
-        <v>88</v>
+        <v>292</v>
       </c>
       <c r="M154" s="4">
         <v>0</v>
@@ -8711,40 +8711,40 @@
     </row>
     <row r="155">
       <c r="A155" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="I155" s="4" t="s">
-        <v>129</v>
+        <v>293</v>
       </c>
       <c r="J155" s="4">
         <v>90</v>
       </c>
       <c r="K155" s="4" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="L155" s="4" t="s">
-        <v>129</v>
+        <v>293</v>
       </c>
       <c r="M155" s="4">
         <v>0</v>
@@ -8759,40 +8759,40 @@
     </row>
     <row r="156">
       <c r="A156" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H156" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B156" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G156" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H156" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="I156" s="4" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="J156" s="4">
         <v>90</v>
       </c>
       <c r="K156" s="4" t="s">
-        <v>139</v>
+        <v>295</v>
       </c>
       <c r="L156" s="4" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="M156" s="4">
         <v>0</v>
@@ -8807,40 +8807,40 @@
     </row>
     <row r="157">
       <c r="A157" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B157" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H157" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C157" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E157" s="3" t="s">
+      <c r="I157" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H157" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="I157" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="J157" s="4">
         <v>90</v>
       </c>
       <c r="K157" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>118</v>
+        <v>297</v>
       </c>
       <c r="M157" s="4">
         <v>0</v>
@@ -8855,40 +8855,40 @@
     </row>
     <row r="158">
       <c r="A158" s="3" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="I158" s="4" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="J158" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K158" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="L158" s="4" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="M158" s="4">
         <v>0</v>
@@ -8903,40 +8903,40 @@
     </row>
     <row r="159">
       <c r="A159" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="I159" s="4" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="J159" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K159" s="4" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="L159" s="4" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="M159" s="4">
         <v>0</v>
@@ -8951,40 +8951,40 @@
     </row>
     <row r="160">
       <c r="A160" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>42</v>
+        <v>298</v>
       </c>
       <c r="I160" s="4" t="s">
-        <v>145</v>
+        <v>299</v>
       </c>
       <c r="J160" s="4">
         <v>90</v>
       </c>
       <c r="K160" s="4" t="s">
-        <v>42</v>
+        <v>298</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>145</v>
+        <v>299</v>
       </c>
       <c r="M160" s="4">
         <v>0</v>
@@ -8999,40 +8999,40 @@
     </row>
     <row r="161">
       <c r="A161" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="I161" s="4" t="s">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="J161" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K161" s="4" t="s">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="L161" s="4" t="s">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="M161" s="4">
         <v>0</v>
@@ -9047,40 +9047,40 @@
     </row>
     <row r="162">
       <c r="A162" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="I162" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J162" s="4">
         <v>90</v>
       </c>
       <c r="K162" s="4" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="L162" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="M162" s="4">
         <v>0</v>
@@ -9095,40 +9095,40 @@
     </row>
     <row r="163">
       <c r="A163" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>303</v>
+        <v>131</v>
       </c>
       <c r="I163" s="4" t="s">
-        <v>58</v>
+        <v>301</v>
       </c>
       <c r="J163" s="4">
         <v>90</v>
       </c>
       <c r="K163" s="4" t="s">
-        <v>303</v>
+        <v>131</v>
       </c>
       <c r="L163" s="4" t="s">
-        <v>58</v>
+        <v>301</v>
       </c>
       <c r="M163" s="4">
         <v>0</v>
@@ -9143,40 +9143,40 @@
     </row>
     <row r="164">
       <c r="A164" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>121</v>
+        <v>302</v>
       </c>
       <c r="I164" s="4" t="s">
-        <v>122</v>
+        <v>303</v>
       </c>
       <c r="J164" s="4">
         <v>90</v>
       </c>
       <c r="K164" s="4" t="s">
-        <v>121</v>
+        <v>302</v>
       </c>
       <c r="L164" s="4" t="s">
-        <v>122</v>
+        <v>303</v>
       </c>
       <c r="M164" s="4">
         <v>0</v>
@@ -9186,6 +9186,54 @@
         <v>26</v>
       </c>
       <c r="P164" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H165" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I165" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J165" s="4">
+        <v>480</v>
+      </c>
+      <c r="K165" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L165" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M165" s="4">
+        <v>0</v>
+      </c>
+      <c r="N165" s="3"/>
+      <c r="O165" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P165" s="4" t="s">
         <v>27</v>
       </c>
     </row>

--- a/data/hrm_sync_actual_1.xlsx
+++ b/data/hrm_sync_actual_1.xlsx
@@ -98,6 +98,27 @@
   </si>
   <si>
     <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>05/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 15:30:00</t>
   </si>
   <si>
     <t>Chưa duyệt</t>
@@ -671,25 +692,25 @@
         <v>31</v>
       </c>
       <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="J4" s="8">
         <v>90</v>
       </c>
       <c r="K4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
@@ -699,26 +720,56 @@
         <v>26</v>
       </c>
       <c r="P4" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1">
+      <c r="A5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="8">
+        <v>90</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7"/>
+      <c r="O5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7"/>

--- a/data/hrm_sync_actual_1.xlsx
+++ b/data/hrm_sync_actual_1.xlsx
@@ -121,7 +121,7 @@
     <t>05/10/2026 15:30:00</t>
   </si>
   <si>
-    <t>Chưa duyệt</t>
+    <t>Chờ cấp trên gian tiếp</t>
   </si>
   <si>
     <t>02020947</t>
@@ -143,6 +143,51 @@
   </si>
   <si>
     <t>02/10/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>vận hành máy nghiền</t>
+  </si>
+  <si>
+    <t>05/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận hành máy nghiền </t>
+  </si>
+  <si>
+    <t>06/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>06/10/2026 15:30:00</t>
   </si>
 </sst>
 </file>
@@ -772,94 +817,244 @@
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="A6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="8">
+        <v>90</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="A7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" s="8">
+        <v>90</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
+      <c r="O7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="A8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="8">
+        <v>90</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
+      <c r="O8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="8">
+        <v>90</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
       <c r="N9" s="7"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
+      <c r="O9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="A10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="8">
+        <v>90</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
       <c r="N10" s="7"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
+      <c r="O10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7"/>

--- a/data/hrm_sync_actual_1.xlsx
+++ b/data/hrm_sync_actual_1.xlsx
@@ -70,60 +70,75 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>08/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gian tiếp</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>05/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
     <t>02317843</t>
   </si>
   <si>
     <t>Đinh Hoàng Phúc</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
     <t>T Extrusion</t>
   </si>
   <si>
     <t>Tăng ca bảo trì</t>
   </si>
   <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
     <t>03/10/2026 07:45:00</t>
   </si>
   <si>
     <t>03/10/2026 16:30:00</t>
   </si>
   <si>
-    <t>Bằng KH</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền</t>
-  </si>
-  <si>
-    <t>05/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
     <t>02020947</t>
   </si>
   <si>
@@ -143,6 +158,69 @@
   </si>
   <si>
     <t>02/10/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>vận hành máy nghiền</t>
+  </si>
+  <si>
+    <t>05/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận hành máy nghiền </t>
+  </si>
+  <si>
+    <t>06/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>06/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>06/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 15:30:00</t>
   </si>
 </sst>
 </file>
@@ -656,7 +734,7 @@
         <v>25</v>
       </c>
       <c r="J3" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>24</v>
@@ -686,10 +764,10 @@
         <v>19</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>22</v>
@@ -698,19 +776,19 @@
         <v>23</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="J4" s="8">
         <v>90</v>
       </c>
       <c r="K4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
@@ -720,45 +798,45 @@
         <v>26</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="J5" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M5" s="8">
         <v>0</v>
@@ -768,206 +846,536 @@
         <v>26</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="A6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="8">
+        <v>90</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="A7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" s="8">
+        <v>90</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
+      <c r="O7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="A8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="8">
+        <v>90</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
+      <c r="O8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="8">
+        <v>90</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
       <c r="N9" s="7"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
+      <c r="O9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="A10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="8">
+        <v>90</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
       <c r="N10" s="7"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
+      <c r="O10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" s="2" customFormat="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="A11" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="8">
+        <v>90</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
       <c r="N11" s="7"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
+      <c r="O11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="12" s="2" customFormat="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
+      <c r="A12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="8">
+        <v>90</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
       <c r="N12" s="7"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
+      <c r="O12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" s="2" customFormat="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
+      <c r="A13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="8">
+        <v>90</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
       <c r="N13" s="7"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
+      <c r="O13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="14" s="2" customFormat="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
+      <c r="A14" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" s="8">
+        <v>90</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
       <c r="N14" s="7"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
+      <c r="O14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
+      <c r="A15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" s="8">
+        <v>90</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
       <c r="N15" s="7"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
+      <c r="O15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="16" s="2" customFormat="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
+      <c r="A16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="8">
+        <v>90</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0</v>
+      </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
+      <c r="O16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7"/>

--- a/data/hrm_sync_actual_1.xlsx
+++ b/data/hrm_sync_actual_1.xlsx
@@ -70,73 +70,358 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>Tăng ca bảo trì</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>03/10/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>03/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>Bằng KH</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>05/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 15:30:00</t>
+  </si>
+  <si>
     <t>02645241</t>
   </si>
   <si>
     <t>Nguyễn Đình Hoàng</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
     <t>hỗ trợ nghiền</t>
   </si>
   <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
     <t>08/10/2026 12:30:00</t>
   </si>
   <si>
     <t>08/10/2026 14:00:00</t>
   </si>
   <si>
-    <t>Bằng KH</t>
+    <t>09/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>10/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>11/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca3</t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>10/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>10/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca 1 </t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>TĂNG CA SẢN XUẤT (ca1)</t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>10/10/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>10/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02021159</t>
+  </si>
+  <si>
+    <t>Trần Vương</t>
+  </si>
+  <si>
+    <t>01921560</t>
+  </si>
+  <si>
+    <t>Trần Quang Hiệu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất. </t>
+  </si>
+  <si>
+    <t>02645250</t>
+  </si>
+  <si>
+    <t>Trần Xuân Bắc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHORT Trục </t>
+  </si>
+  <si>
+    <t>02325365</t>
+  </si>
+  <si>
+    <t>Trần Minh Nhật</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất (ca 3)</t>
+  </si>
+  <si>
+    <t>02325310</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Hậu</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ( ca 3)</t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
+  </si>
+  <si>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>Lắp đặt rack hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>02619486</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
+  </si>
+  <si>
+    <t>Lắp đặt thiết bị</t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca2 </t>
+  </si>
+  <si>
+    <t>02325374</t>
+  </si>
+  <si>
+    <t>Trương Văn Tình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>Tăng ca setup line đùn PL21</t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ sản xuất (Ca1)</t>
+  </si>
+  <si>
+    <t>02022149</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Mạnh</t>
+  </si>
+  <si>
+    <t>02022158</t>
+  </si>
+  <si>
+    <t>Bùi Lê Đức Minh</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất (ca 2)</t>
+  </si>
+  <si>
+    <t>02516134</t>
+  </si>
+  <si>
+    <t>Ngô Xuân Nghĩa</t>
+  </si>
+  <si>
+    <t>Thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>02021131</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Anh</t>
+  </si>
+  <si>
+    <t>02224288</t>
+  </si>
+  <si>
+    <t>Võ Văn Dương</t>
+  </si>
+  <si>
+    <t>02645269</t>
+  </si>
+  <si>
+    <t>Lê Thanh Toàn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca 3. </t>
+  </si>
+  <si>
+    <t>12/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>12/10/2026 15:30:00</t>
   </si>
   <si>
     <t>Chờ cấp trên gian tiếp</t>
   </si>
   <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền</t>
-  </si>
-  <si>
-    <t>05/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>Tăng ca bảo trì</t>
-  </si>
-  <si>
-    <t>03/10/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>03/10/2026 16:30:00</t>
+    <t>12/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>12/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 15:30:00</t>
   </si>
   <si>
     <t>02020947</t>
@@ -160,6 +445,27 @@
     <t>02/10/2026 18:00:00</t>
   </si>
   <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>tang ca van hanh may nghien</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận hành máy nghiền </t>
+  </si>
+  <si>
+    <t>05/10/2026 12:30:00</t>
+  </si>
+  <si>
     <t>02644057</t>
   </si>
   <si>
@@ -181,46 +487,97 @@
     <t>06/10/2026 22:00:00</t>
   </si>
   <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận hành máy nghiền </t>
-  </si>
-  <si>
     <t>06/10/2026 12:30:00</t>
   </si>
   <si>
     <t>06/10/2026 14:00:00</t>
   </si>
   <si>
+    <t>06/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>07/10/2026 15:30:00</t>
+  </si>
+  <si>
     <t>07/10/2026 12:30:00</t>
   </si>
   <si>
-    <t>07/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>tang ca van hanh may nghien</t>
-  </si>
-  <si>
-    <t>06/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>07/10/2026 15:30:00</t>
+    <t>08/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 22:00:00</t>
   </si>
   <si>
     <t>08/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>Tăng Cường Sản Xuất</t>
+  </si>
+  <si>
+    <t>02622116</t>
+  </si>
+  <si>
+    <t>Trịnh Nhựt Khánh</t>
+  </si>
+  <si>
+    <t>tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>02228947</t>
+  </si>
+  <si>
+    <t>Phạm Lê Minh Tân</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>Tăng cường sản xuất</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>tǎng ca Vân hành máy nghiên</t>
   </si>
 </sst>
 </file>
@@ -734,7 +1091,7 @@
         <v>25</v>
       </c>
       <c r="J3" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>24</v>
@@ -764,10 +1121,10 @@
         <v>19</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>22</v>
@@ -776,19 +1133,19 @@
         <v>23</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" s="8">
         <v>90</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M4" s="8">
         <v>0</v>
@@ -798,7 +1155,7 @@
         <v>26</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1">
@@ -812,10 +1169,10 @@
         <v>19</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>22</v>
@@ -824,19 +1181,19 @@
         <v>23</v>
       </c>
       <c r="H5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>39</v>
-      </c>
       <c r="J5" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="K5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="M5" s="8">
         <v>0</v>
@@ -846,45 +1203,45 @@
         <v>26</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="J6" s="8">
         <v>90</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M6" s="8">
         <v>0</v>
@@ -894,45 +1251,45 @@
         <v>26</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J7" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M7" s="8">
         <v>0</v>
@@ -942,45 +1299,45 @@
         <v>26</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="F8" s="7" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J8" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M8" s="8">
         <v>0</v>
@@ -990,45 +1347,45 @@
         <v>26</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J9" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M9" s="8">
         <v>0</v>
@@ -1038,7 +1395,7 @@
         <v>26</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1">
@@ -1052,31 +1409,31 @@
         <v>19</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>56</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J10" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M10" s="8">
         <v>0</v>
@@ -1086,45 +1443,45 @@
         <v>26</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="J11" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M11" s="8">
         <v>0</v>
@@ -1134,45 +1491,45 @@
         <v>26</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="J12" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="M12" s="8">
         <v>0</v>
@@ -1182,45 +1539,45 @@
         <v>26</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="J13" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="M13" s="8">
         <v>0</v>
@@ -1230,45 +1587,45 @@
         <v>26</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="J14" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="M14" s="8">
         <v>0</v>
@@ -1278,45 +1635,45 @@
         <v>26</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="J15" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="M15" s="8">
         <v>0</v>
@@ -1326,45 +1683,45 @@
         <v>26</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J16" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="M16" s="8">
         <v>0</v>
@@ -1374,242 +1731,2456 @@
         <v>26</v>
       </c>
       <c r="P16" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1">
+      <c r="A17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="8">
+        <v>480</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="7"/>
+      <c r="O17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1">
+      <c r="A18" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="8">
+        <v>480</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0</v>
+      </c>
+      <c r="N18" s="7"/>
+      <c r="O18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1">
+      <c r="A19" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="8">
+        <v>480</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="7"/>
+      <c r="O19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1">
+      <c r="A20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20" s="8">
+        <v>480</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0</v>
+      </c>
+      <c r="N20" s="7"/>
+      <c r="O20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1">
+      <c r="A21" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" s="8">
+        <v>480</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+      <c r="N21" s="7"/>
+      <c r="O21" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1">
+      <c r="A22" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" s="8">
+        <v>480</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M22" s="8">
+        <v>0</v>
+      </c>
+      <c r="N22" s="7"/>
+      <c r="O22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1">
+      <c r="A23" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J23" s="8">
+        <v>480</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
+      <c r="N23" s="7"/>
+      <c r="O23" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1">
+      <c r="A24" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J24" s="8">
+        <v>480</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
+      <c r="N24" s="7"/>
+      <c r="O24" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1">
+      <c r="A25" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" s="8">
+        <v>480</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+      <c r="N25" s="7"/>
+      <c r="O25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P25" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1">
+      <c r="A26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" s="8">
+        <v>480</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M26" s="8">
+        <v>0</v>
+      </c>
+      <c r="N26" s="7"/>
+      <c r="O26" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1">
+      <c r="A27" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J27" s="8">
+        <v>480</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+      <c r="N27" s="7"/>
+      <c r="O27" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1">
+      <c r="A28" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J28" s="8">
+        <v>480</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M28" s="8">
+        <v>0</v>
+      </c>
+      <c r="N28" s="7"/>
+      <c r="O28" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1">
+      <c r="A29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J29" s="8">
+        <v>480</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
+      <c r="N29" s="7"/>
+      <c r="O29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P29" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30" s="4">
+        <v>480</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+      <c r="O30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J31" s="4">
+        <v>480</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+      <c r="O31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J32" s="4">
+        <v>480</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M32" s="4">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J33" s="4">
+        <v>480</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="M33" s="4">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" s="4">
+        <v>480</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M34" s="4">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J35" s="4">
+        <v>480</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3"/>
+      <c r="O35" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J36" s="4">
+        <v>480</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M36" s="4">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3"/>
+      <c r="O36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J37" s="4">
+        <v>90</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="M37" s="4">
+        <v>0</v>
+      </c>
+      <c r="N37" s="3"/>
+      <c r="O37" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J38" s="4">
+        <v>90</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="M38" s="4">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3"/>
+      <c r="O38" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="J39" s="4">
+        <v>90</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="M39" s="4">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3"/>
+      <c r="O39" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="J40" s="4">
+        <v>90</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3"/>
+      <c r="O40" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J41" s="4">
+        <v>90</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M41" s="4">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3"/>
+      <c r="O41" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" s="2" customFormat="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-    </row>
-    <row r="18" s="2" customFormat="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-    </row>
-    <row r="19" s="2" customFormat="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-    </row>
-    <row r="20" s="2" customFormat="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-    </row>
-    <row r="21" s="2" customFormat="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-    </row>
-    <row r="22" s="2" customFormat="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-    </row>
-    <row r="23" s="2" customFormat="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-    </row>
-    <row r="24" s="2" customFormat="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-    </row>
-    <row r="25" s="2" customFormat="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-    </row>
-    <row r="26" s="2" customFormat="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-    </row>
-    <row r="27" s="2" customFormat="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-    </row>
-    <row r="28" s="2" customFormat="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-    </row>
-    <row r="29" s="2" customFormat="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
+      <c r="J42" s="4">
+        <v>90</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M42" s="4">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+      <c r="O42" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J43" s="4">
+        <v>90</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M43" s="4">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3"/>
+      <c r="O43" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J44" s="4">
+        <v>90</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="M44" s="4">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+      <c r="O44" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="J45" s="4">
+        <v>90</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="M45" s="4">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3"/>
+      <c r="O45" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="J46" s="4">
+        <v>90</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M46" s="4">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3"/>
+      <c r="O46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="J47" s="4">
+        <v>90</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="M47" s="4">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+      <c r="O47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J48" s="4">
+        <v>90</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="M48" s="4">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3"/>
+      <c r="O48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="J49" s="4">
+        <v>90</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="M49" s="4">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3"/>
+      <c r="O49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J50" s="4">
+        <v>90</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="M50" s="4">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+      <c r="O50" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J51" s="4">
+        <v>90</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="M51" s="4">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+      <c r="O51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J52" s="4">
+        <v>90</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="M52" s="4">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3"/>
+      <c r="O52" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J53" s="4">
+        <v>90</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M53" s="4">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+      <c r="O53" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="J54" s="4">
+        <v>90</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="M54" s="4">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3"/>
+      <c r="O54" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="J55" s="4">
+        <v>90</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="M55" s="4">
+        <v>0</v>
+      </c>
+      <c r="N55" s="3"/>
+      <c r="O55" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J56" s="4">
+        <v>90</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M56" s="4">
+        <v>0</v>
+      </c>
+      <c r="N56" s="3"/>
+      <c r="O56" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J57" s="4">
+        <v>480</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M57" s="4">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3"/>
+      <c r="O57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J58" s="4">
+        <v>480</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M58" s="4">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3"/>
+      <c r="O58" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P58" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J59" s="4">
+        <v>480</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M59" s="4">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3"/>
+      <c r="O59" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P59" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J60" s="4">
+        <v>480</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M60" s="4">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3"/>
+      <c r="O60" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P60" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J61" s="4">
+        <v>480</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M61" s="4">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+      <c r="O61" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J62" s="4">
+        <v>480</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M62" s="4">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3"/>
+      <c r="O62" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J63" s="4">
+        <v>480</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M63" s="4">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+      <c r="O63" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P63" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J64" s="4">
+        <v>480</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M64" s="4">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+      <c r="O64" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P64" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J65" s="4">
+        <v>480</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M65" s="4">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+      <c r="O65" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J66" s="4">
+        <v>90</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="M66" s="4">
+        <v>0</v>
+      </c>
+      <c r="N66" s="3"/>
+      <c r="O66" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P66" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J67" s="4">
+        <v>90</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="M67" s="4">
+        <v>0</v>
+      </c>
+      <c r="N67" s="3"/>
+      <c r="O67" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P67" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/hrm_sync_actual_1.xlsx
+++ b/data/hrm_sync_actual_1.xlsx
@@ -403,25 +403,184 @@
     <t>12/10/2026 15:30:00</t>
   </si>
   <si>
+    <t>12/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>12/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca2</t>
+  </si>
+  <si>
+    <t>17/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>17/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>setup line PL01</t>
+  </si>
+  <si>
+    <t>17/10/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>17/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất. ca 3 </t>
+  </si>
+  <si>
+    <t>18/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca thứ 7 Short </t>
+  </si>
+  <si>
+    <t>17/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Lắp rack hỗ trợ sản xuất.</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất Ca 3</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 3</t>
+  </si>
+  <si>
+    <t>02660444</t>
+  </si>
+  <si>
+    <t>Võ Minh Đức</t>
+  </si>
+  <si>
+    <t>đóng thùng thành phẩm vận chuyển hàng ng</t>
+  </si>
+  <si>
+    <t>02661799</t>
+  </si>
+  <si>
+    <t>Đặng Lê Minh Tài</t>
+  </si>
+  <si>
+    <t>vận chuyển nguyên vật liệu</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 1)</t>
+  </si>
+  <si>
+    <t>Tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>02223535</t>
+  </si>
+  <si>
+    <t>Nguyễn Quốc</t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ sản xuất (Ca2)</t>
+  </si>
+  <si>
+    <t>02325295</t>
+  </si>
+  <si>
+    <t>Lưu Văn Đủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất  (ca2)</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 3</t>
+  </si>
+  <si>
+    <t>Tăng ca triển khai bản vẽ cover máy nghiền.</t>
+  </si>
+  <si>
+    <t>21/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>21/10/2026 18:00:00</t>
+  </si>
+  <si>
     <t>Chờ cấp trên gian tiếp</t>
   </si>
   <si>
-    <t>12/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>12/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>13/10/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>13/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>13/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>13/10/2026 15:30:00</t>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>22/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/10/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Tăng ca hoàn thiện bản vẽ cover máy nghiền.</t>
   </si>
   <si>
     <t>02020947</t>
@@ -430,15 +589,9 @@
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
     <t xml:space="preserve">di chuyển nguyên vật liệu nghiền </t>
   </si>
   <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
     <t>02/10/2026 16:30:00</t>
   </si>
   <si>
@@ -578,6 +731,63 @@
   </si>
   <si>
     <t>tǎng ca Vân hành máy nghiên</t>
+  </si>
+  <si>
+    <t>13/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca Vân hành máy nghiêń</t>
+  </si>
+  <si>
+    <t>14/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02224358</t>
+  </si>
+  <si>
+    <t>Hoàng Trung Hiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca3 tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>02226596</t>
+  </si>
+  <si>
+    <t>Đoàn Văn Dương</t>
+  </si>
+  <si>
+    <t>Vận hành máy nghiền</t>
   </si>
 </sst>
 </file>
@@ -2739,7 +2949,7 @@
         <v>26</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
@@ -2765,19 +2975,19 @@
         <v>23</v>
       </c>
       <c r="H38" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I38" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="J38" s="4">
         <v>90</v>
       </c>
       <c r="K38" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="L38" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="M38" s="4">
         <v>0</v>
@@ -2813,19 +3023,19 @@
         <v>23</v>
       </c>
       <c r="H39" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="J39" s="4">
         <v>90</v>
       </c>
       <c r="K39" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="L39" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="M39" s="4">
         <v>0</v>
@@ -2835,7 +3045,7 @@
         <v>26</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
@@ -2861,19 +3071,19 @@
         <v>23</v>
       </c>
       <c r="H40" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="J40" s="4">
         <v>90</v>
       </c>
       <c r="K40" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="L40" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="M40" s="4">
         <v>0</v>
@@ -2883,45 +3093,45 @@
         <v>26</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="J41" s="4">
         <v>90</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="M41" s="4">
         <v>0</v>
@@ -2936,40 +3146,40 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="J42" s="4">
         <v>90</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="M42" s="4">
         <v>0</v>
@@ -2984,40 +3194,40 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>146</v>
+        <v>35</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="F43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I43" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="J43" s="4">
         <v>90</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="M43" s="4">
         <v>0</v>
@@ -3032,40 +3242,40 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J44" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="M44" s="4">
         <v>0</v>
@@ -3080,40 +3290,40 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="J45" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="M45" s="4">
         <v>0</v>
@@ -3128,40 +3338,40 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="F46" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="J46" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="M46" s="4">
         <v>0</v>
@@ -3176,40 +3386,40 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="J47" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="M47" s="4">
         <v>0</v>
@@ -3224,40 +3434,40 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="J48" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M48" s="4">
         <v>0</v>
@@ -3272,40 +3482,40 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="J49" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="M49" s="4">
         <v>0</v>
@@ -3320,40 +3530,40 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="J50" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="M50" s="4">
         <v>0</v>
@@ -3368,40 +3578,40 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="J51" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="M51" s="4">
         <v>0</v>
@@ -3416,40 +3626,40 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="I52" s="4" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="J52" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="M52" s="4">
         <v>0</v>
@@ -3464,40 +3674,40 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="J53" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="M53" s="4">
         <v>0</v>
@@ -3512,40 +3722,40 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="J54" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="M54" s="4">
         <v>0</v>
@@ -3560,40 +3770,40 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="J55" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="M55" s="4">
         <v>0</v>
@@ -3608,40 +3818,40 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>147</v>
+        <v>56</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="J56" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="M56" s="4">
         <v>0</v>
@@ -3656,40 +3866,40 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="J57" s="4">
         <v>480</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="M57" s="4">
         <v>0</v>
@@ -3704,40 +3914,40 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="J58" s="4">
         <v>480</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="M58" s="4">
         <v>0</v>
@@ -3752,40 +3962,40 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="J59" s="4">
         <v>480</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="M59" s="4">
         <v>0</v>
@@ -3800,40 +4010,40 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>176</v>
+        <v>49</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>177</v>
+        <v>50</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>178</v>
+        <v>51</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="J60" s="4">
         <v>480</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="M60" s="4">
         <v>0</v>
@@ -3848,40 +4058,40 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>179</v>
+        <v>96</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>44</v>
+        <v>148</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="J61" s="4">
         <v>480</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>44</v>
+        <v>148</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="M61" s="4">
         <v>0</v>
@@ -3896,40 +4106,40 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="J62" s="4">
         <v>480</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="M62" s="4">
         <v>0</v>
@@ -3944,40 +4154,40 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="J63" s="4">
         <v>480</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="M63" s="4">
         <v>0</v>
@@ -3992,40 +4202,40 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="J64" s="4">
         <v>480</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="M64" s="4">
         <v>0</v>
@@ -4040,40 +4250,40 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>149</v>
+        <v>28</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="J65" s="4">
         <v>480</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="M65" s="4">
         <v>0</v>
@@ -4088,40 +4298,40 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>186</v>
+        <v>118</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="J66" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="M66" s="4">
         <v>0</v>
@@ -4136,40 +4346,40 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="J67" s="4">
         <v>90</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="M67" s="4">
         <v>0</v>
@@ -4179,6 +4389,2454 @@
         <v>26</v>
       </c>
       <c r="P67" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="J68" s="4">
+        <v>90</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M68" s="4">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+      <c r="O68" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P68" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="J69" s="4">
+        <v>90</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M69" s="4">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+      <c r="O69" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P69" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J70" s="4">
+        <v>90</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M70" s="4">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+      <c r="O70" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P70" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J71" s="4">
+        <v>90</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M71" s="4">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+      <c r="O71" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J72" s="4">
+        <v>90</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M72" s="4">
+        <v>0</v>
+      </c>
+      <c r="N72" s="3"/>
+      <c r="O72" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P72" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="J73" s="4">
+        <v>90</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M73" s="4">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+      <c r="O73" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P73" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="J74" s="4">
+        <v>90</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="L74" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="M74" s="4">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+      <c r="O74" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P74" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="J75" s="4">
+        <v>90</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="M75" s="4">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+      <c r="O75" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P75" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="J76" s="4">
+        <v>90</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="M76" s="4">
+        <v>0</v>
+      </c>
+      <c r="N76" s="3"/>
+      <c r="O76" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P76" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J77" s="4">
+        <v>90</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="M77" s="4">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+      <c r="O77" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="J78" s="4">
+        <v>90</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="M78" s="4">
+        <v>0</v>
+      </c>
+      <c r="N78" s="3"/>
+      <c r="O78" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J79" s="4">
+        <v>90</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="M79" s="4">
+        <v>0</v>
+      </c>
+      <c r="N79" s="3"/>
+      <c r="O79" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P79" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="J80" s="4">
+        <v>90</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="M80" s="4">
+        <v>0</v>
+      </c>
+      <c r="N80" s="3"/>
+      <c r="O80" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P80" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="J81" s="4">
+        <v>90</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="M81" s="4">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3"/>
+      <c r="O81" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P81" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J82" s="4">
+        <v>90</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M82" s="4">
+        <v>0</v>
+      </c>
+      <c r="N82" s="3"/>
+      <c r="O82" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P82" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="J83" s="4">
+        <v>90</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="M83" s="4">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3"/>
+      <c r="O83" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P83" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="J84" s="4">
+        <v>90</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="M84" s="4">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+      <c r="O84" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P84" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J85" s="4">
+        <v>90</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M85" s="4">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+      <c r="O85" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P85" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J86" s="4">
+        <v>480</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M86" s="4">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+      <c r="O86" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P86" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J87" s="4">
+        <v>480</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M87" s="4">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+      <c r="O87" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P87" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J88" s="4">
+        <v>480</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M88" s="4">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+      <c r="O88" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P88" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J89" s="4">
+        <v>480</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M89" s="4">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3"/>
+      <c r="O89" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P89" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J90" s="4">
+        <v>480</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L90" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M90" s="4">
+        <v>0</v>
+      </c>
+      <c r="N90" s="3"/>
+      <c r="O90" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P90" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J91" s="4">
+        <v>480</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L91" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M91" s="4">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3"/>
+      <c r="O91" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P91" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J92" s="4">
+        <v>480</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M92" s="4">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+      <c r="O92" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P92" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J93" s="4">
+        <v>480</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M93" s="4">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+      <c r="O93" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P93" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J94" s="4">
+        <v>480</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L94" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M94" s="4">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3"/>
+      <c r="O94" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P94" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J95" s="4">
+        <v>90</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="L95" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="M95" s="4">
+        <v>0</v>
+      </c>
+      <c r="N95" s="3"/>
+      <c r="O95" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P95" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J96" s="4">
+        <v>90</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="L96" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="M96" s="4">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+      <c r="O96" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P96" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="J97" s="4">
+        <v>90</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="M97" s="4">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+      <c r="O97" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P97" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="J98" s="4">
+        <v>90</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="M98" s="4">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+      <c r="O98" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P98" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J99" s="4">
+        <v>90</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="L99" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="M99" s="4">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+      <c r="O99" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P99" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="J100" s="4">
+        <v>90</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L100" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M100" s="4">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3"/>
+      <c r="O100" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P100" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="J101" s="4">
+        <v>90</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="L101" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="M101" s="4">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+      <c r="O101" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P101" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="J102" s="4">
+        <v>90</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="L102" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="M102" s="4">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3"/>
+      <c r="O102" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P102" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="J103" s="4">
+        <v>90</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="M103" s="4">
+        <v>0</v>
+      </c>
+      <c r="N103" s="3"/>
+      <c r="O103" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P103" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="J104" s="4">
+        <v>90</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="L104" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="M104" s="4">
+        <v>0</v>
+      </c>
+      <c r="N104" s="3"/>
+      <c r="O104" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P104" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J105" s="4">
+        <v>90</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="L105" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="M105" s="4">
+        <v>0</v>
+      </c>
+      <c r="N105" s="3"/>
+      <c r="O105" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P105" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J106" s="4">
+        <v>90</v>
+      </c>
+      <c r="K106" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="L106" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M106" s="4">
+        <v>0</v>
+      </c>
+      <c r="N106" s="3"/>
+      <c r="O106" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P106" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="J107" s="4">
+        <v>90</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="L107" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="M107" s="4">
+        <v>0</v>
+      </c>
+      <c r="N107" s="3"/>
+      <c r="O107" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P107" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I108" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J108" s="4">
+        <v>480</v>
+      </c>
+      <c r="K108" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="L108" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="M108" s="4">
+        <v>0</v>
+      </c>
+      <c r="N108" s="3"/>
+      <c r="O108" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P108" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J109" s="4">
+        <v>480</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="L109" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="M109" s="4">
+        <v>0</v>
+      </c>
+      <c r="N109" s="3"/>
+      <c r="O109" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P109" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J110" s="4">
+        <v>480</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="L110" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M110" s="4">
+        <v>0</v>
+      </c>
+      <c r="N110" s="3"/>
+      <c r="O110" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P110" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J111" s="4">
+        <v>480</v>
+      </c>
+      <c r="K111" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="L111" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M111" s="4">
+        <v>0</v>
+      </c>
+      <c r="N111" s="3"/>
+      <c r="O111" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P111" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J112" s="4">
+        <v>480</v>
+      </c>
+      <c r="K112" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="L112" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="M112" s="4">
+        <v>0</v>
+      </c>
+      <c r="N112" s="3"/>
+      <c r="O112" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P112" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J113" s="4">
+        <v>480</v>
+      </c>
+      <c r="K113" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="L113" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="M113" s="4">
+        <v>0</v>
+      </c>
+      <c r="N113" s="3"/>
+      <c r="O113" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P113" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I114" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J114" s="4">
+        <v>480</v>
+      </c>
+      <c r="K114" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="L114" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="M114" s="4">
+        <v>0</v>
+      </c>
+      <c r="N114" s="3"/>
+      <c r="O114" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P114" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I115" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J115" s="4">
+        <v>480</v>
+      </c>
+      <c r="K115" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="L115" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M115" s="4">
+        <v>0</v>
+      </c>
+      <c r="N115" s="3"/>
+      <c r="O115" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P115" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I116" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J116" s="4">
+        <v>480</v>
+      </c>
+      <c r="K116" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="L116" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="M116" s="4">
+        <v>0</v>
+      </c>
+      <c r="N116" s="3"/>
+      <c r="O116" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P116" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J117" s="4">
+        <v>480</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="L117" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="M117" s="4">
+        <v>0</v>
+      </c>
+      <c r="N117" s="3"/>
+      <c r="O117" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P117" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I118" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J118" s="4">
+        <v>480</v>
+      </c>
+      <c r="K118" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="L118" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="M118" s="4">
+        <v>0</v>
+      </c>
+      <c r="N118" s="3"/>
+      <c r="O118" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P118" s="4" t="s">
         <v>27</v>
       </c>
     </row>
